--- a/DRIVE TRHU BASE.xlsx
+++ b/DRIVE TRHU BASE.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="8910"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="8910" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Drive HME" sheetId="1" r:id="rId1"/>
@@ -13,7 +13,7 @@
     <sheet name="Cotizaciones" sheetId="7" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Atenciones 2025'!$A$1:$N$73</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Atenciones 2025'!$A$1:$M$73</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1779" uniqueCount="251">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1621" uniqueCount="245">
   <si>
     <t>N°</t>
   </si>
@@ -231,9 +231,6 @@
     <t>DETALLE</t>
   </si>
   <si>
-    <t>TIPOLOGIA</t>
-  </si>
-  <si>
     <t>DIURNO/NOCTURNO</t>
   </si>
   <si>
@@ -258,9 +255,6 @@
     <t xml:space="preserve">SE REPORTARON AUTOS FANTASMA </t>
   </si>
   <si>
-    <t>T3</t>
-  </si>
-  <si>
     <t>HORARIO DE OFICINA</t>
   </si>
   <si>
@@ -285,9 +279,6 @@
     <t>INTERMITENCIA DE RED</t>
   </si>
   <si>
-    <t>T2</t>
-  </si>
-  <si>
     <t>MIRAFLORES</t>
   </si>
   <si>
@@ -303,9 +294,6 @@
     <t>CAMBIO DE BATERIA Y CARGADOR ABERIADOS</t>
   </si>
   <si>
-    <t>T1</t>
-  </si>
-  <si>
     <t>LA MOLINA</t>
   </si>
   <si>
@@ -318,9 +306,6 @@
     <t>FEBRERO</t>
   </si>
   <si>
-    <t>T4</t>
-  </si>
-  <si>
     <t>VERIFICAR SI TIENDA CUENTA CON HME CLOUD Y VALIDAR CONECCION Y CABLEADO CORRECTOS</t>
   </si>
   <si>
@@ -739,9 +724,6 @@
   </si>
   <si>
     <t>KFC 160</t>
-  </si>
-  <si>
-    <t>AV. LA MARINA 2000, SAN MIGUEL</t>
   </si>
   <si>
     <t>KFC206</t>
@@ -1015,7 +997,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="61">
+  <cellXfs count="60">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1176,9 +1158,6 @@
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1532,7 +1511,7 @@
         <v>42</v>
       </c>
       <c r="R1" s="9" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="S1" s="9" t="s">
         <v>47</v>
@@ -1633,7 +1612,7 @@
         <v>23</v>
       </c>
       <c r="Y2" s="31" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="Z2" s="31" t="s">
         <v>54</v>
@@ -1758,7 +1737,7 @@
         <v>1</v>
       </c>
       <c r="N4" s="30" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="O4" s="30">
         <v>1</v>
@@ -1992,7 +1971,7 @@
         <v>1</v>
       </c>
       <c r="N7" s="30" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="O7" s="30">
         <v>1</v>
@@ -2025,7 +2004,7 @@
         <v>23</v>
       </c>
       <c r="Y7" s="31" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="Z7" s="31" t="s">
         <v>53</v>
@@ -2105,7 +2084,7 @@
         <v>23</v>
       </c>
       <c r="Y8" s="35" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="Z8" s="35" t="s">
         <v>50</v>
@@ -2185,7 +2164,7 @@
         <v>23</v>
       </c>
       <c r="Y9" s="31" t="s">
-        <v>250</v>
+        <v>244</v>
       </c>
       <c r="Z9" s="31" t="s">
         <v>56</v>
@@ -2199,10 +2178,10 @@
         <v>16</v>
       </c>
       <c r="C10" s="29" t="s">
-        <v>239</v>
+        <v>233</v>
       </c>
       <c r="D10" s="29" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="E10" s="30">
         <v>3</v>
@@ -2265,10 +2244,10 @@
         <v>23</v>
       </c>
       <c r="Y10" s="31" t="s">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="Z10" s="31" t="s">
-        <v>241</v>
+        <v>235</v>
       </c>
     </row>
     <row r="11" spans="1:26" s="32" customFormat="1" x14ac:dyDescent="0.2">
@@ -2437,7 +2416,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N94"/>
+  <dimension ref="A1:M94"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.28515625" style="13" bestFit="1" customWidth="1"/>
@@ -2449,12 +2428,11 @@
     <col min="8" max="8" width="15.42578125" style="13" customWidth="1"/>
     <col min="9" max="9" width="21.28515625" style="13" customWidth="1"/>
     <col min="10" max="10" width="47.85546875" style="13" customWidth="1"/>
-    <col min="11" max="11" width="11.42578125" style="13"/>
-    <col min="12" max="12" width="21.7109375" style="13" customWidth="1"/>
-    <col min="13" max="16384" width="11.42578125" style="13"/>
+    <col min="11" max="11" width="21.7109375" style="13" customWidth="1"/>
+    <col min="12" max="16384" width="11.42578125" style="13"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
         <v>59</v>
       </c>
@@ -2491,14 +2469,11 @@
       <c r="L1" s="11" t="s">
         <v>69</v>
       </c>
-      <c r="M1" s="11" t="s">
+      <c r="M1" s="12" t="s">
         <v>70</v>
       </c>
-      <c r="N1" s="12" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="2" spans="1:14" ht="139.5" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:13" ht="139.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="26">
         <v>1</v>
       </c>
@@ -2506,13 +2481,13 @@
         <v>36</v>
       </c>
       <c r="C2" s="14" t="s">
+        <v>71</v>
+      </c>
+      <c r="D2" s="26" t="s">
         <v>72</v>
       </c>
-      <c r="D2" s="26" t="s">
+      <c r="E2" s="26" t="s">
         <v>73</v>
-      </c>
-      <c r="E2" s="26" t="s">
-        <v>74</v>
       </c>
       <c r="F2" s="15">
         <v>45659</v>
@@ -2521,42 +2496,39 @@
         <v>2</v>
       </c>
       <c r="H2" s="25" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="I2" s="15" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="J2" s="25" t="s">
-        <v>112</v>
-      </c>
-      <c r="K2" s="17" t="s">
-        <v>77</v>
-      </c>
-      <c r="L2" s="18" t="s">
-        <v>78</v>
-      </c>
-      <c r="M2" s="26" t="s">
-        <v>79</v>
-      </c>
-      <c r="N2" s="17" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14" ht="139.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>107</v>
+      </c>
+      <c r="K2" s="18" t="s">
+        <v>76</v>
+      </c>
+      <c r="L2" s="26" t="s">
+        <v>77</v>
+      </c>
+      <c r="M2" s="17" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" ht="139.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="26">
         <v>2</v>
       </c>
       <c r="B3" s="26" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="C3" s="26" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D3" s="26" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E3" s="26" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F3" s="15">
         <v>45663</v>
@@ -2565,28 +2537,25 @@
         <v>1</v>
       </c>
       <c r="H3" s="25" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="I3" s="15" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="J3" s="25" t="s">
-        <v>113</v>
-      </c>
-      <c r="K3" s="17" t="s">
-        <v>77</v>
-      </c>
-      <c r="L3" s="18" t="s">
-        <v>78</v>
-      </c>
-      <c r="M3" s="26" t="s">
-        <v>79</v>
-      </c>
-      <c r="N3" s="17" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14" ht="147" customHeight="1" x14ac:dyDescent="0.25">
+        <v>108</v>
+      </c>
+      <c r="K3" s="18" t="s">
+        <v>76</v>
+      </c>
+      <c r="L3" s="26" t="s">
+        <v>77</v>
+      </c>
+      <c r="M3" s="17" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" ht="147" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="26">
         <v>3</v>
       </c>
@@ -2594,13 +2563,13 @@
         <v>19</v>
       </c>
       <c r="C4" s="26" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D4" s="26" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E4" s="26" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F4" s="15">
         <v>45663</v>
@@ -2609,42 +2578,39 @@
         <v>2</v>
       </c>
       <c r="H4" s="25" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="I4" s="15" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="J4" s="17" t="s">
-        <v>114</v>
-      </c>
-      <c r="K4" s="26" t="s">
-        <v>86</v>
-      </c>
-      <c r="L4" s="18" t="s">
-        <v>78</v>
-      </c>
-      <c r="M4" s="26" t="s">
-        <v>79</v>
-      </c>
-      <c r="N4" s="17" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14" ht="147.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>109</v>
+      </c>
+      <c r="K4" s="18" t="s">
+        <v>76</v>
+      </c>
+      <c r="L4" s="26" t="s">
+        <v>77</v>
+      </c>
+      <c r="M4" s="17" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" ht="147.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="26">
         <v>4</v>
       </c>
       <c r="B5" s="26" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="C5" s="26" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="D5" s="26" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="E5" s="26" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F5" s="15">
         <v>45663</v>
@@ -2653,28 +2619,25 @@
         <v>2</v>
       </c>
       <c r="H5" s="25" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="I5" s="15" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="J5" s="17" t="s">
-        <v>114</v>
-      </c>
-      <c r="K5" s="26" t="s">
-        <v>86</v>
-      </c>
-      <c r="L5" s="18" t="s">
-        <v>78</v>
-      </c>
-      <c r="M5" s="26" t="s">
-        <v>79</v>
-      </c>
-      <c r="N5" s="17" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14" ht="150" customHeight="1" x14ac:dyDescent="0.25">
+        <v>109</v>
+      </c>
+      <c r="K5" s="18" t="s">
+        <v>76</v>
+      </c>
+      <c r="L5" s="26" t="s">
+        <v>77</v>
+      </c>
+      <c r="M5" s="17" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" ht="150" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="26">
         <v>5</v>
       </c>
@@ -2682,13 +2645,13 @@
         <v>24</v>
       </c>
       <c r="C6" s="26" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="D6" s="26" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="E6" s="26" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F6" s="15">
         <v>45665</v>
@@ -2697,28 +2660,25 @@
         <v>2</v>
       </c>
       <c r="H6" s="25" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="I6" s="15" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="J6" s="17" t="s">
-        <v>114</v>
-      </c>
-      <c r="K6" s="26" t="s">
-        <v>86</v>
-      </c>
-      <c r="L6" s="18" t="s">
-        <v>78</v>
-      </c>
-      <c r="M6" s="26" t="s">
-        <v>79</v>
-      </c>
-      <c r="N6" s="17" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14" ht="114" customHeight="1" x14ac:dyDescent="0.25">
+        <v>109</v>
+      </c>
+      <c r="K6" s="18" t="s">
+        <v>76</v>
+      </c>
+      <c r="L6" s="26" t="s">
+        <v>77</v>
+      </c>
+      <c r="M6" s="17" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" ht="114" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="26">
         <v>6</v>
       </c>
@@ -2726,13 +2686,13 @@
         <v>19</v>
       </c>
       <c r="C7" s="26" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D7" s="26" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E7" s="26" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F7" s="15">
         <v>45667</v>
@@ -2741,42 +2701,39 @@
         <v>2</v>
       </c>
       <c r="H7" s="25" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="I7" s="25" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="J7" s="17" t="s">
-        <v>115</v>
-      </c>
-      <c r="K7" s="26" t="s">
-        <v>86</v>
-      </c>
-      <c r="L7" s="18" t="s">
-        <v>78</v>
-      </c>
-      <c r="M7" s="26" t="s">
-        <v>79</v>
-      </c>
-      <c r="N7" s="17" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14" ht="141" customHeight="1" x14ac:dyDescent="0.25">
+        <v>110</v>
+      </c>
+      <c r="K7" s="18" t="s">
+        <v>76</v>
+      </c>
+      <c r="L7" s="26" t="s">
+        <v>77</v>
+      </c>
+      <c r="M7" s="17" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" ht="141" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="26">
         <v>7</v>
       </c>
       <c r="B8" s="26" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="C8" s="26" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D8" s="26" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="E8" s="26" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F8" s="15">
         <v>45667</v>
@@ -2785,42 +2742,39 @@
         <v>2</v>
       </c>
       <c r="H8" s="25" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="I8" s="15" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="J8" s="25" t="s">
-        <v>112</v>
-      </c>
-      <c r="K8" s="17" t="s">
-        <v>77</v>
-      </c>
-      <c r="L8" s="18" t="s">
-        <v>78</v>
-      </c>
-      <c r="M8" s="26" t="s">
-        <v>79</v>
-      </c>
-      <c r="N8" s="17" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14" ht="146.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>107</v>
+      </c>
+      <c r="K8" s="18" t="s">
+        <v>76</v>
+      </c>
+      <c r="L8" s="26" t="s">
+        <v>77</v>
+      </c>
+      <c r="M8" s="17" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" ht="146.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="26">
         <v>8</v>
       </c>
       <c r="B9" s="26" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="C9" s="26" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="D9" s="26" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="E9" s="26" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F9" s="15">
         <v>45672</v>
@@ -2829,28 +2783,25 @@
         <v>2</v>
       </c>
       <c r="H9" s="25" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="I9" s="15" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="J9" s="17" t="s">
-        <v>116</v>
-      </c>
-      <c r="K9" s="26" t="s">
-        <v>92</v>
-      </c>
-      <c r="L9" s="18" t="s">
-        <v>78</v>
-      </c>
-      <c r="M9" s="26" t="s">
-        <v>79</v>
-      </c>
-      <c r="N9" s="17" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14" ht="143.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>111</v>
+      </c>
+      <c r="K9" s="18" t="s">
+        <v>76</v>
+      </c>
+      <c r="L9" s="26" t="s">
+        <v>77</v>
+      </c>
+      <c r="M9" s="17" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" ht="143.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="26">
         <v>9</v>
       </c>
@@ -2858,13 +2809,13 @@
         <v>21</v>
       </c>
       <c r="C10" s="17" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="D10" s="26" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="E10" s="26" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F10" s="15">
         <v>45672</v>
@@ -2873,28 +2824,25 @@
         <v>2</v>
       </c>
       <c r="H10" s="25" t="s">
+        <v>74</v>
+      </c>
+      <c r="I10" s="15" t="s">
         <v>75</v>
       </c>
-      <c r="I10" s="15" t="s">
-        <v>76</v>
-      </c>
       <c r="J10" s="25" t="s">
-        <v>112</v>
-      </c>
-      <c r="K10" s="17" t="s">
-        <v>77</v>
-      </c>
-      <c r="L10" s="18" t="s">
-        <v>78</v>
-      </c>
-      <c r="M10" s="26" t="s">
-        <v>79</v>
-      </c>
-      <c r="N10" s="17" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14" ht="214.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>107</v>
+      </c>
+      <c r="K10" s="18" t="s">
+        <v>76</v>
+      </c>
+      <c r="L10" s="26" t="s">
+        <v>77</v>
+      </c>
+      <c r="M10" s="17" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" ht="214.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="26">
         <v>10</v>
       </c>
@@ -2902,13 +2850,13 @@
         <v>27</v>
       </c>
       <c r="C11" s="26" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D11" s="26" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="E11" s="26" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F11" s="15">
         <v>45672</v>
@@ -2917,28 +2865,25 @@
         <v>2</v>
       </c>
       <c r="H11" s="25" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="I11" s="15" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="J11" s="25" t="s">
-        <v>112</v>
-      </c>
-      <c r="K11" s="17" t="s">
-        <v>77</v>
-      </c>
-      <c r="L11" s="18" t="s">
-        <v>78</v>
-      </c>
-      <c r="M11" s="26" t="s">
-        <v>79</v>
-      </c>
-      <c r="N11" s="17" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14" ht="168.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>107</v>
+      </c>
+      <c r="K11" s="18" t="s">
+        <v>76</v>
+      </c>
+      <c r="L11" s="26" t="s">
+        <v>77</v>
+      </c>
+      <c r="M11" s="17" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" ht="168.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="26">
         <v>11</v>
       </c>
@@ -2946,13 +2891,13 @@
         <v>36</v>
       </c>
       <c r="C12" s="14" t="s">
+        <v>71</v>
+      </c>
+      <c r="D12" s="26" t="s">
         <v>72</v>
       </c>
-      <c r="D12" s="26" t="s">
+      <c r="E12" s="26" t="s">
         <v>73</v>
-      </c>
-      <c r="E12" s="26" t="s">
-        <v>74</v>
       </c>
       <c r="F12" s="15">
         <v>45674</v>
@@ -2961,28 +2906,25 @@
         <v>2</v>
       </c>
       <c r="H12" s="25" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="I12" s="15" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="J12" s="17" t="s">
-        <v>116</v>
-      </c>
-      <c r="K12" s="26" t="s">
-        <v>92</v>
-      </c>
-      <c r="L12" s="18" t="s">
-        <v>78</v>
-      </c>
-      <c r="M12" s="26" t="s">
-        <v>79</v>
-      </c>
-      <c r="N12" s="17" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14" ht="156.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>111</v>
+      </c>
+      <c r="K12" s="18" t="s">
+        <v>76</v>
+      </c>
+      <c r="L12" s="26" t="s">
+        <v>77</v>
+      </c>
+      <c r="M12" s="17" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" ht="156.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="26">
         <v>12</v>
       </c>
@@ -2990,13 +2932,13 @@
         <v>36</v>
       </c>
       <c r="C13" s="14" t="s">
+        <v>71</v>
+      </c>
+      <c r="D13" s="26" t="s">
         <v>72</v>
       </c>
-      <c r="D13" s="26" t="s">
+      <c r="E13" s="26" t="s">
         <v>73</v>
-      </c>
-      <c r="E13" s="26" t="s">
-        <v>74</v>
       </c>
       <c r="F13" s="15">
         <v>45679</v>
@@ -3005,28 +2947,25 @@
         <v>2</v>
       </c>
       <c r="H13" s="25" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="I13" s="15" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="J13" s="25" t="s">
-        <v>117</v>
-      </c>
-      <c r="K13" s="17" t="s">
-        <v>77</v>
-      </c>
-      <c r="L13" s="18" t="s">
-        <v>78</v>
-      </c>
-      <c r="M13" s="26" t="s">
-        <v>79</v>
-      </c>
-      <c r="N13" s="17" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14" ht="192.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>112</v>
+      </c>
+      <c r="K13" s="18" t="s">
+        <v>76</v>
+      </c>
+      <c r="L13" s="26" t="s">
+        <v>77</v>
+      </c>
+      <c r="M13" s="17" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" ht="192.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="26">
         <v>13</v>
       </c>
@@ -3034,13 +2973,13 @@
         <v>33</v>
       </c>
       <c r="C14" s="17" t="s">
+        <v>71</v>
+      </c>
+      <c r="D14" s="26" t="s">
         <v>72</v>
       </c>
-      <c r="D14" s="26" t="s">
+      <c r="E14" s="26" t="s">
         <v>73</v>
-      </c>
-      <c r="E14" s="26" t="s">
-        <v>74</v>
       </c>
       <c r="F14" s="15">
         <v>45681</v>
@@ -3049,28 +2988,25 @@
         <v>2</v>
       </c>
       <c r="H14" s="25" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="I14" s="15" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="J14" s="25" t="s">
-        <v>118</v>
-      </c>
-      <c r="K14" s="17" t="s">
-        <v>92</v>
-      </c>
-      <c r="L14" s="18" t="s">
-        <v>78</v>
-      </c>
-      <c r="M14" s="26" t="s">
-        <v>79</v>
-      </c>
-      <c r="N14" s="17" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14" ht="194.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>113</v>
+      </c>
+      <c r="K14" s="18" t="s">
+        <v>76</v>
+      </c>
+      <c r="L14" s="26" t="s">
+        <v>77</v>
+      </c>
+      <c r="M14" s="17" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" ht="194.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="26">
         <v>14</v>
       </c>
@@ -3078,13 +3014,13 @@
         <v>36</v>
       </c>
       <c r="C15" s="14" t="s">
+        <v>71</v>
+      </c>
+      <c r="D15" s="26" t="s">
         <v>72</v>
       </c>
-      <c r="D15" s="26" t="s">
+      <c r="E15" s="26" t="s">
         <v>73</v>
-      </c>
-      <c r="E15" s="26" t="s">
-        <v>74</v>
       </c>
       <c r="F15" s="15">
         <v>45687</v>
@@ -3093,28 +3029,25 @@
         <v>2</v>
       </c>
       <c r="H15" s="25" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="I15" s="15" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="J15" s="25" t="s">
-        <v>119</v>
-      </c>
-      <c r="K15" s="17" t="s">
-        <v>86</v>
-      </c>
-      <c r="L15" s="18" t="s">
-        <v>78</v>
-      </c>
-      <c r="M15" s="26" t="s">
-        <v>79</v>
-      </c>
-      <c r="N15" s="17" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14" ht="149.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>114</v>
+      </c>
+      <c r="K15" s="18" t="s">
+        <v>76</v>
+      </c>
+      <c r="L15" s="26" t="s">
+        <v>77</v>
+      </c>
+      <c r="M15" s="17" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" ht="149.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="26">
         <v>15</v>
       </c>
@@ -3122,13 +3055,13 @@
         <v>21</v>
       </c>
       <c r="C16" s="17" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="D16" s="26" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="E16" s="26" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="F16" s="15">
         <v>45693</v>
@@ -3137,28 +3070,25 @@
         <v>2</v>
       </c>
       <c r="H16" s="25" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="I16" s="15" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="J16" s="25" t="s">
-        <v>112</v>
-      </c>
-      <c r="K16" s="17" t="s">
-        <v>77</v>
-      </c>
-      <c r="L16" s="18" t="s">
-        <v>78</v>
-      </c>
-      <c r="M16" s="26" t="s">
-        <v>79</v>
-      </c>
-      <c r="N16" s="17" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="17" spans="1:14" ht="145.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>107</v>
+      </c>
+      <c r="K16" s="18" t="s">
+        <v>76</v>
+      </c>
+      <c r="L16" s="26" t="s">
+        <v>77</v>
+      </c>
+      <c r="M16" s="17" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" ht="145.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="26">
         <v>16</v>
       </c>
@@ -3166,13 +3096,13 @@
         <v>19</v>
       </c>
       <c r="C17" s="26" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D17" s="26" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E17" s="26" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="F17" s="15">
         <v>45694</v>
@@ -3181,28 +3111,25 @@
         <v>2</v>
       </c>
       <c r="H17" s="25" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="I17" s="15" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="J17" s="25" t="s">
-        <v>112</v>
-      </c>
-      <c r="K17" s="17" t="s">
-        <v>77</v>
-      </c>
-      <c r="L17" s="18" t="s">
-        <v>78</v>
-      </c>
-      <c r="M17" s="26" t="s">
-        <v>79</v>
-      </c>
-      <c r="N17" s="17" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="18" spans="1:14" ht="153.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>107</v>
+      </c>
+      <c r="K17" s="18" t="s">
+        <v>76</v>
+      </c>
+      <c r="L17" s="26" t="s">
+        <v>77</v>
+      </c>
+      <c r="M17" s="17" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" ht="153.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="26">
         <v>17</v>
       </c>
@@ -3210,13 +3137,13 @@
         <v>21</v>
       </c>
       <c r="C18" s="17" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="D18" s="26" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="E18" s="26" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="F18" s="15">
         <v>45695</v>
@@ -3225,42 +3152,39 @@
         <v>2</v>
       </c>
       <c r="H18" s="25" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="I18" s="15" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="J18" s="17" t="s">
-        <v>120</v>
-      </c>
-      <c r="K18" s="26" t="s">
-        <v>97</v>
-      </c>
-      <c r="L18" s="19" t="s">
-        <v>78</v>
-      </c>
-      <c r="M18" s="26" t="s">
-        <v>79</v>
-      </c>
-      <c r="N18" s="17" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="19" spans="1:14" ht="153" customHeight="1" x14ac:dyDescent="0.25">
+        <v>115</v>
+      </c>
+      <c r="K18" s="19" t="s">
+        <v>76</v>
+      </c>
+      <c r="L18" s="26" t="s">
+        <v>77</v>
+      </c>
+      <c r="M18" s="17" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" ht="153" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="26">
         <v>18</v>
       </c>
       <c r="B19" s="26" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="C19" s="26" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D19" s="26" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="E19" s="26" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="F19" s="15">
         <v>45699</v>
@@ -3269,42 +3193,39 @@
         <v>2</v>
       </c>
       <c r="H19" s="25" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="I19" s="25" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="J19" s="17" t="s">
-        <v>115</v>
-      </c>
-      <c r="K19" s="26" t="s">
-        <v>86</v>
-      </c>
-      <c r="L19" s="18" t="s">
-        <v>78</v>
-      </c>
-      <c r="M19" s="26" t="s">
-        <v>79</v>
-      </c>
-      <c r="N19" s="17" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="20" spans="1:14" ht="127.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>110</v>
+      </c>
+      <c r="K19" s="18" t="s">
+        <v>76</v>
+      </c>
+      <c r="L19" s="26" t="s">
+        <v>77</v>
+      </c>
+      <c r="M19" s="17" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" ht="127.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="26">
         <v>19</v>
       </c>
       <c r="B20" s="26" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="C20" s="26" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="D20" s="26" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="E20" s="26" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="F20" s="15">
         <v>45705</v>
@@ -3313,42 +3234,39 @@
         <v>2</v>
       </c>
       <c r="H20" s="25" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="I20" s="25" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="J20" s="17" t="s">
-        <v>120</v>
-      </c>
-      <c r="K20" s="26" t="s">
-        <v>97</v>
-      </c>
-      <c r="L20" s="19" t="s">
-        <v>78</v>
-      </c>
-      <c r="M20" s="26" t="s">
-        <v>79</v>
-      </c>
-      <c r="N20" s="17" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="21" spans="1:14" ht="135" x14ac:dyDescent="0.25">
+        <v>115</v>
+      </c>
+      <c r="K20" s="19" t="s">
+        <v>76</v>
+      </c>
+      <c r="L20" s="26" t="s">
+        <v>77</v>
+      </c>
+      <c r="M20" s="17" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" ht="135" x14ac:dyDescent="0.25">
       <c r="A21" s="26">
         <v>20</v>
       </c>
       <c r="B21" s="26" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="C21" s="26" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="D21" s="26" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="E21" s="26" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="F21" s="15">
         <v>45715</v>
@@ -3357,42 +3275,39 @@
         <v>2</v>
       </c>
       <c r="H21" s="25" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="I21" s="25" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="J21" s="17" t="s">
-        <v>115</v>
-      </c>
-      <c r="K21" s="26" t="s">
-        <v>86</v>
-      </c>
-      <c r="L21" s="18" t="s">
-        <v>78</v>
-      </c>
-      <c r="M21" s="26" t="s">
-        <v>79</v>
-      </c>
-      <c r="N21" s="17" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="22" spans="1:14" ht="155.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>110</v>
+      </c>
+      <c r="K21" s="18" t="s">
+        <v>76</v>
+      </c>
+      <c r="L21" s="26" t="s">
+        <v>77</v>
+      </c>
+      <c r="M21" s="17" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" ht="155.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="26">
         <v>21</v>
       </c>
       <c r="B22" s="26" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="C22" s="26" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D22" s="26" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="E22" s="26" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="F22" s="15">
         <v>45723</v>
@@ -3401,42 +3316,39 @@
         <v>2</v>
       </c>
       <c r="H22" s="25" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="I22" s="15" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="J22" s="25" t="s">
-        <v>112</v>
-      </c>
-      <c r="K22" s="17" t="s">
-        <v>77</v>
-      </c>
-      <c r="L22" s="18" t="s">
-        <v>78</v>
-      </c>
-      <c r="M22" s="26" t="s">
-        <v>79</v>
-      </c>
-      <c r="N22" s="17" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="23" spans="1:14" ht="120" x14ac:dyDescent="0.25">
+        <v>107</v>
+      </c>
+      <c r="K22" s="18" t="s">
+        <v>76</v>
+      </c>
+      <c r="L22" s="26" t="s">
+        <v>77</v>
+      </c>
+      <c r="M22" s="17" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" ht="120" x14ac:dyDescent="0.25">
       <c r="A23" s="26">
         <v>22</v>
       </c>
       <c r="B23" s="26" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="C23" s="26" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="D23" s="26" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="E23" s="26" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="F23" s="15">
         <v>45723</v>
@@ -3445,42 +3357,39 @@
         <v>1</v>
       </c>
       <c r="H23" s="25" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="I23" s="15" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="J23" s="25" t="s">
-        <v>112</v>
-      </c>
-      <c r="K23" s="17" t="s">
-        <v>77</v>
-      </c>
-      <c r="L23" s="18" t="s">
-        <v>78</v>
-      </c>
-      <c r="M23" s="26" t="s">
-        <v>79</v>
-      </c>
-      <c r="N23" s="17" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="24" spans="1:14" ht="120" x14ac:dyDescent="0.25">
+        <v>107</v>
+      </c>
+      <c r="K23" s="18" t="s">
+        <v>76</v>
+      </c>
+      <c r="L23" s="26" t="s">
+        <v>77</v>
+      </c>
+      <c r="M23" s="17" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" ht="120" x14ac:dyDescent="0.25">
       <c r="A24" s="26">
         <v>23</v>
       </c>
       <c r="B24" s="26" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="C24" s="26" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D24" s="26" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="E24" s="26" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="F24" s="15">
         <v>45724</v>
@@ -3489,42 +3398,39 @@
         <v>1</v>
       </c>
       <c r="H24" s="25" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="I24" s="15" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="J24" s="25" t="s">
-        <v>112</v>
-      </c>
-      <c r="K24" s="17" t="s">
-        <v>77</v>
-      </c>
-      <c r="L24" s="18" t="s">
-        <v>78</v>
-      </c>
-      <c r="M24" s="26" t="s">
-        <v>79</v>
-      </c>
-      <c r="N24" s="17" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="25" spans="1:14" ht="120" x14ac:dyDescent="0.25">
+        <v>107</v>
+      </c>
+      <c r="K24" s="18" t="s">
+        <v>76</v>
+      </c>
+      <c r="L24" s="26" t="s">
+        <v>77</v>
+      </c>
+      <c r="M24" s="17" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" ht="120" x14ac:dyDescent="0.25">
       <c r="A25" s="26">
         <v>24</v>
       </c>
       <c r="B25" s="26" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="C25" s="26" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="D25" s="26" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="E25" s="26" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="F25" s="15">
         <v>45726</v>
@@ -3533,42 +3439,39 @@
         <v>1</v>
       </c>
       <c r="H25" s="25" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="I25" s="15" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="J25" s="25" t="s">
-        <v>113</v>
-      </c>
-      <c r="K25" s="17" t="s">
-        <v>77</v>
-      </c>
-      <c r="L25" s="18" t="s">
-        <v>78</v>
-      </c>
-      <c r="M25" s="26" t="s">
-        <v>79</v>
-      </c>
-      <c r="N25" s="17" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="26" spans="1:14" ht="120" x14ac:dyDescent="0.25">
+        <v>108</v>
+      </c>
+      <c r="K25" s="18" t="s">
+        <v>76</v>
+      </c>
+      <c r="L25" s="26" t="s">
+        <v>77</v>
+      </c>
+      <c r="M25" s="17" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" ht="120" x14ac:dyDescent="0.25">
       <c r="A26" s="26">
         <v>25</v>
       </c>
       <c r="B26" s="26" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="C26" s="26" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="D26" s="26" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="E26" s="26" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="F26" s="15">
         <v>45732</v>
@@ -3577,42 +3480,39 @@
         <v>1</v>
       </c>
       <c r="H26" s="25" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="I26" s="15" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="J26" s="25" t="s">
-        <v>113</v>
-      </c>
-      <c r="K26" s="17" t="s">
-        <v>77</v>
-      </c>
-      <c r="L26" s="18" t="s">
-        <v>78</v>
-      </c>
-      <c r="M26" s="26" t="s">
-        <v>79</v>
-      </c>
-      <c r="N26" s="17" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="27" spans="1:14" ht="120" x14ac:dyDescent="0.25">
+        <v>108</v>
+      </c>
+      <c r="K26" s="18" t="s">
+        <v>76</v>
+      </c>
+      <c r="L26" s="26" t="s">
+        <v>77</v>
+      </c>
+      <c r="M26" s="17" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" ht="120" x14ac:dyDescent="0.25">
       <c r="A27" s="26">
         <v>26</v>
       </c>
       <c r="B27" s="26" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="C27" s="26" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D27" s="26" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="E27" s="26" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="F27" s="15">
         <v>45736</v>
@@ -3621,42 +3521,39 @@
         <v>1</v>
       </c>
       <c r="H27" s="25" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="I27" s="15" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="J27" s="25" t="s">
-        <v>113</v>
-      </c>
-      <c r="K27" s="17" t="s">
-        <v>77</v>
-      </c>
-      <c r="L27" s="18" t="s">
-        <v>78</v>
-      </c>
-      <c r="M27" s="26" t="s">
-        <v>79</v>
-      </c>
-      <c r="N27" s="17" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="28" spans="1:14" ht="120" x14ac:dyDescent="0.25">
+        <v>108</v>
+      </c>
+      <c r="K27" s="18" t="s">
+        <v>76</v>
+      </c>
+      <c r="L27" s="26" t="s">
+        <v>77</v>
+      </c>
+      <c r="M27" s="17" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" ht="120" x14ac:dyDescent="0.25">
       <c r="A28" s="26">
         <v>27</v>
       </c>
       <c r="B28" s="26" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="C28" s="26" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="D28" s="26" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="E28" s="26" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="F28" s="15">
         <v>45739</v>
@@ -3665,42 +3562,39 @@
         <v>1</v>
       </c>
       <c r="H28" s="25" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="I28" s="15" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="J28" s="25" t="s">
-        <v>113</v>
-      </c>
-      <c r="K28" s="17" t="s">
-        <v>77</v>
-      </c>
-      <c r="L28" s="18" t="s">
-        <v>78</v>
-      </c>
-      <c r="M28" s="26" t="s">
-        <v>79</v>
-      </c>
-      <c r="N28" s="17" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="29" spans="1:14" ht="120" x14ac:dyDescent="0.25">
+        <v>108</v>
+      </c>
+      <c r="K28" s="18" t="s">
+        <v>76</v>
+      </c>
+      <c r="L28" s="26" t="s">
+        <v>77</v>
+      </c>
+      <c r="M28" s="17" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" ht="120" x14ac:dyDescent="0.25">
       <c r="A29" s="26">
         <v>28</v>
       </c>
       <c r="B29" s="26" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="C29" s="26" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D29" s="26" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="E29" s="26" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="F29" s="15">
         <v>45743</v>
@@ -3709,42 +3603,39 @@
         <v>1</v>
       </c>
       <c r="H29" s="25" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="I29" s="15" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="J29" s="25" t="s">
-        <v>113</v>
-      </c>
-      <c r="K29" s="17" t="s">
-        <v>77</v>
-      </c>
-      <c r="L29" s="18" t="s">
-        <v>78</v>
-      </c>
-      <c r="M29" s="26" t="s">
-        <v>79</v>
-      </c>
-      <c r="N29" s="17" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="30" spans="1:14" ht="120" x14ac:dyDescent="0.25">
+        <v>108</v>
+      </c>
+      <c r="K29" s="18" t="s">
+        <v>76</v>
+      </c>
+      <c r="L29" s="26" t="s">
+        <v>77</v>
+      </c>
+      <c r="M29" s="17" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" ht="120" x14ac:dyDescent="0.25">
       <c r="A30" s="26">
         <v>29</v>
       </c>
       <c r="B30" s="26" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="C30" s="26" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="D30" s="26" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="E30" s="26" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="F30" s="15">
         <v>45743</v>
@@ -3753,42 +3644,39 @@
         <v>1</v>
       </c>
       <c r="H30" s="25" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="I30" s="15" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="J30" s="25" t="s">
-        <v>113</v>
-      </c>
-      <c r="K30" s="17" t="s">
-        <v>77</v>
-      </c>
-      <c r="L30" s="18" t="s">
-        <v>78</v>
-      </c>
-      <c r="M30" s="26" t="s">
-        <v>79</v>
-      </c>
-      <c r="N30" s="17" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="31" spans="1:14" ht="105" x14ac:dyDescent="0.25">
+        <v>108</v>
+      </c>
+      <c r="K30" s="18" t="s">
+        <v>76</v>
+      </c>
+      <c r="L30" s="26" t="s">
+        <v>77</v>
+      </c>
+      <c r="M30" s="17" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" ht="105" x14ac:dyDescent="0.25">
       <c r="A31" s="26">
         <v>30</v>
       </c>
       <c r="B31" s="26" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="C31" s="26" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="D31" s="26" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="E31" s="26" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="F31" s="15">
         <v>45747</v>
@@ -3797,42 +3685,39 @@
         <v>2</v>
       </c>
       <c r="H31" s="25" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="I31" s="15" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="J31" s="25" t="s">
-        <v>121</v>
-      </c>
-      <c r="K31" s="17" t="s">
-        <v>97</v>
-      </c>
-      <c r="L31" s="18" t="s">
-        <v>78</v>
-      </c>
-      <c r="M31" s="26" t="s">
-        <v>79</v>
-      </c>
-      <c r="N31" s="17" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="32" spans="1:14" ht="120" x14ac:dyDescent="0.25">
+        <v>116</v>
+      </c>
+      <c r="K31" s="18" t="s">
+        <v>76</v>
+      </c>
+      <c r="L31" s="26" t="s">
+        <v>77</v>
+      </c>
+      <c r="M31" s="17" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" ht="120" x14ac:dyDescent="0.25">
       <c r="A32" s="26">
         <v>31</v>
       </c>
       <c r="B32" s="26" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="C32" s="26" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="D32" s="26" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="E32" s="26" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="F32" s="15">
         <v>45749</v>
@@ -3841,42 +3726,39 @@
         <v>1</v>
       </c>
       <c r="H32" s="25" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="I32" s="15" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="J32" s="25" t="s">
-        <v>113</v>
-      </c>
-      <c r="K32" s="17" t="s">
-        <v>77</v>
-      </c>
-      <c r="L32" s="18" t="s">
-        <v>78</v>
-      </c>
-      <c r="M32" s="26" t="s">
-        <v>79</v>
-      </c>
-      <c r="N32" s="17" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="33" spans="1:14" ht="105" x14ac:dyDescent="0.25">
+        <v>108</v>
+      </c>
+      <c r="K32" s="18" t="s">
+        <v>76</v>
+      </c>
+      <c r="L32" s="26" t="s">
+        <v>77</v>
+      </c>
+      <c r="M32" s="17" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" ht="105" x14ac:dyDescent="0.25">
       <c r="A33" s="26">
         <v>32</v>
       </c>
       <c r="B33" s="26" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="C33" s="26" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="D33" s="26" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="E33" s="26" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="F33" s="15">
         <v>45751</v>
@@ -3885,28 +3767,25 @@
         <v>1</v>
       </c>
       <c r="H33" s="25" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="I33" s="15" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="J33" s="25" t="s">
-        <v>122</v>
-      </c>
-      <c r="K33" s="17" t="s">
-        <v>97</v>
-      </c>
-      <c r="L33" s="18" t="s">
-        <v>78</v>
-      </c>
-      <c r="M33" s="26" t="s">
-        <v>79</v>
-      </c>
-      <c r="N33" s="17" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="34" spans="1:14" ht="120" x14ac:dyDescent="0.25">
+        <v>117</v>
+      </c>
+      <c r="K33" s="18" t="s">
+        <v>76</v>
+      </c>
+      <c r="L33" s="26" t="s">
+        <v>77</v>
+      </c>
+      <c r="M33" s="17" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" ht="120" x14ac:dyDescent="0.25">
       <c r="A34" s="26">
         <v>33</v>
       </c>
@@ -3914,13 +3793,13 @@
         <v>27</v>
       </c>
       <c r="C34" s="26" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D34" s="26" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="E34" s="26" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="F34" s="15">
         <v>45751</v>
@@ -3929,42 +3808,39 @@
         <v>1</v>
       </c>
       <c r="H34" s="25" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="I34" s="15" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="J34" s="25" t="s">
-        <v>112</v>
-      </c>
-      <c r="K34" s="17" t="s">
-        <v>97</v>
-      </c>
-      <c r="L34" s="18" t="s">
-        <v>78</v>
-      </c>
-      <c r="M34" s="26" t="s">
-        <v>79</v>
-      </c>
-      <c r="N34" s="17" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="35" spans="1:14" ht="120" x14ac:dyDescent="0.25">
+        <v>107</v>
+      </c>
+      <c r="K34" s="18" t="s">
+        <v>76</v>
+      </c>
+      <c r="L34" s="26" t="s">
+        <v>77</v>
+      </c>
+      <c r="M34" s="17" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13" ht="120" x14ac:dyDescent="0.25">
       <c r="A35" s="26">
         <v>34</v>
       </c>
       <c r="B35" s="26" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="C35" s="26" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D35" s="26" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="E35" s="26" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="F35" s="15">
         <v>45753</v>
@@ -3973,28 +3849,25 @@
         <v>1</v>
       </c>
       <c r="H35" s="25" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="I35" s="15" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="J35" s="25" t="s">
-        <v>113</v>
-      </c>
-      <c r="K35" s="17" t="s">
-        <v>77</v>
-      </c>
-      <c r="L35" s="18" t="s">
-        <v>78</v>
-      </c>
-      <c r="M35" s="26" t="s">
-        <v>79</v>
-      </c>
-      <c r="N35" s="17" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="36" spans="1:14" ht="120" x14ac:dyDescent="0.25">
+        <v>108</v>
+      </c>
+      <c r="K35" s="18" t="s">
+        <v>76</v>
+      </c>
+      <c r="L35" s="26" t="s">
+        <v>77</v>
+      </c>
+      <c r="M35" s="17" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13" ht="120" x14ac:dyDescent="0.25">
       <c r="A36" s="26">
         <v>35</v>
       </c>
@@ -4002,13 +3875,13 @@
         <v>19</v>
       </c>
       <c r="C36" s="26" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D36" s="26" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E36" s="26" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="F36" s="15">
         <v>45753</v>
@@ -4017,42 +3890,39 @@
         <v>2</v>
       </c>
       <c r="H36" s="25" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="I36" s="15" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="J36" s="25" t="s">
-        <v>112</v>
-      </c>
-      <c r="K36" s="17" t="s">
-        <v>77</v>
-      </c>
-      <c r="L36" s="18" t="s">
-        <v>78</v>
-      </c>
-      <c r="M36" s="26" t="s">
-        <v>79</v>
-      </c>
-      <c r="N36" s="17" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="37" spans="1:14" ht="120" x14ac:dyDescent="0.25">
+        <v>107</v>
+      </c>
+      <c r="K36" s="18" t="s">
+        <v>76</v>
+      </c>
+      <c r="L36" s="26" t="s">
+        <v>77</v>
+      </c>
+      <c r="M36" s="17" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13" ht="120" x14ac:dyDescent="0.25">
       <c r="A37" s="26">
         <v>36</v>
       </c>
       <c r="B37" s="26" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="C37" s="26" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D37" s="26" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="E37" s="26" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="F37" s="15">
         <v>45754</v>
@@ -4061,42 +3931,39 @@
         <v>2</v>
       </c>
       <c r="H37" s="25" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="I37" s="15" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="J37" s="25" t="s">
-        <v>112</v>
-      </c>
-      <c r="K37" s="17" t="s">
-        <v>77</v>
-      </c>
-      <c r="L37" s="18" t="s">
-        <v>78</v>
-      </c>
-      <c r="M37" s="26" t="s">
-        <v>79</v>
-      </c>
-      <c r="N37" s="17" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="38" spans="1:14" ht="120" x14ac:dyDescent="0.25">
+        <v>107</v>
+      </c>
+      <c r="K37" s="18" t="s">
+        <v>76</v>
+      </c>
+      <c r="L37" s="26" t="s">
+        <v>77</v>
+      </c>
+      <c r="M37" s="17" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13" ht="120" x14ac:dyDescent="0.25">
       <c r="A38" s="26">
         <v>37</v>
       </c>
       <c r="B38" s="26" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="C38" s="26" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="D38" s="26" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="E38" s="26" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="F38" s="15">
         <v>45756</v>
@@ -4105,28 +3972,25 @@
         <v>1</v>
       </c>
       <c r="H38" s="25" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="I38" s="15" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="J38" s="25" t="s">
-        <v>113</v>
-      </c>
-      <c r="K38" s="17" t="s">
-        <v>77</v>
-      </c>
-      <c r="L38" s="18" t="s">
-        <v>78</v>
-      </c>
-      <c r="M38" s="26" t="s">
-        <v>79</v>
-      </c>
-      <c r="N38" s="17" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="39" spans="1:14" ht="75" x14ac:dyDescent="0.25">
+        <v>108</v>
+      </c>
+      <c r="K38" s="18" t="s">
+        <v>76</v>
+      </c>
+      <c r="L38" s="26" t="s">
+        <v>77</v>
+      </c>
+      <c r="M38" s="17" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13" ht="75" x14ac:dyDescent="0.25">
       <c r="A39" s="26">
         <v>38</v>
       </c>
@@ -4134,13 +3998,13 @@
         <v>19</v>
       </c>
       <c r="C39" s="26" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D39" s="26" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E39" s="26" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="F39" s="15">
         <v>45761</v>
@@ -4149,28 +4013,25 @@
         <v>1</v>
       </c>
       <c r="H39" s="25" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="I39" s="15" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="J39" s="25" t="s">
-        <v>123</v>
-      </c>
-      <c r="K39" s="17" t="s">
-        <v>77</v>
-      </c>
-      <c r="L39" s="18" t="s">
-        <v>78</v>
-      </c>
-      <c r="M39" s="26" t="s">
-        <v>79</v>
-      </c>
-      <c r="N39" s="17" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="40" spans="1:14" ht="120" x14ac:dyDescent="0.25">
+        <v>118</v>
+      </c>
+      <c r="K39" s="18" t="s">
+        <v>76</v>
+      </c>
+      <c r="L39" s="26" t="s">
+        <v>77</v>
+      </c>
+      <c r="M39" s="17" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13" ht="120" x14ac:dyDescent="0.25">
       <c r="A40" s="26">
         <v>39</v>
       </c>
@@ -4178,13 +4039,13 @@
         <v>27</v>
       </c>
       <c r="C40" s="26" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D40" s="26" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="E40" s="26" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="F40" s="15">
         <v>45761</v>
@@ -4193,28 +4054,25 @@
         <v>1</v>
       </c>
       <c r="H40" s="25" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="I40" s="15" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="J40" s="25" t="s">
-        <v>112</v>
-      </c>
-      <c r="K40" s="17" t="s">
-        <v>77</v>
-      </c>
-      <c r="L40" s="18" t="s">
-        <v>78</v>
-      </c>
-      <c r="M40" s="26" t="s">
-        <v>79</v>
-      </c>
-      <c r="N40" s="17" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="41" spans="1:14" ht="60" x14ac:dyDescent="0.25">
+        <v>107</v>
+      </c>
+      <c r="K40" s="18" t="s">
+        <v>76</v>
+      </c>
+      <c r="L40" s="26" t="s">
+        <v>77</v>
+      </c>
+      <c r="M40" s="17" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13" ht="60" x14ac:dyDescent="0.25">
       <c r="A41" s="26">
         <v>40</v>
       </c>
@@ -4222,13 +4080,13 @@
         <v>27</v>
       </c>
       <c r="C41" s="26" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D41" s="26" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="E41" s="26" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="F41" s="15">
         <v>45762</v>
@@ -4237,28 +4095,25 @@
         <v>1</v>
       </c>
       <c r="H41" s="25" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="I41" s="15" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="J41" s="25" t="s">
-        <v>122</v>
-      </c>
-      <c r="K41" s="17" t="s">
-        <v>97</v>
-      </c>
-      <c r="L41" s="18" t="s">
-        <v>78</v>
-      </c>
-      <c r="M41" s="26" t="s">
-        <v>79</v>
-      </c>
-      <c r="N41" s="17" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="42" spans="1:14" ht="60" x14ac:dyDescent="0.25">
+        <v>117</v>
+      </c>
+      <c r="K41" s="18" t="s">
+        <v>76</v>
+      </c>
+      <c r="L41" s="26" t="s">
+        <v>77</v>
+      </c>
+      <c r="M41" s="17" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="42" spans="1:13" ht="60" x14ac:dyDescent="0.25">
       <c r="A42" s="26">
         <v>41</v>
       </c>
@@ -4266,13 +4121,13 @@
         <v>24</v>
       </c>
       <c r="C42" s="26" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="D42" s="26" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="E42" s="26" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="F42" s="15">
         <v>45762</v>
@@ -4281,28 +4136,25 @@
         <v>1</v>
       </c>
       <c r="H42" s="25" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="I42" s="15" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="J42" s="25" t="s">
-        <v>122</v>
-      </c>
-      <c r="K42" s="17" t="s">
-        <v>97</v>
-      </c>
-      <c r="L42" s="18" t="s">
-        <v>78</v>
-      </c>
-      <c r="M42" s="26" t="s">
-        <v>79</v>
-      </c>
-      <c r="N42" s="17" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="43" spans="1:14" ht="60" x14ac:dyDescent="0.25">
+        <v>117</v>
+      </c>
+      <c r="K42" s="18" t="s">
+        <v>76</v>
+      </c>
+      <c r="L42" s="26" t="s">
+        <v>77</v>
+      </c>
+      <c r="M42" s="17" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="43" spans="1:13" ht="60" x14ac:dyDescent="0.25">
       <c r="A43" s="26">
         <v>42</v>
       </c>
@@ -4310,13 +4162,13 @@
         <v>24</v>
       </c>
       <c r="C43" s="26" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="D43" s="26" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="E43" s="26" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="F43" s="15">
         <v>45763</v>
@@ -4325,42 +4177,39 @@
         <v>1</v>
       </c>
       <c r="H43" s="25" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="I43" s="15" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="J43" s="25" t="s">
-        <v>122</v>
-      </c>
-      <c r="K43" s="17" t="s">
-        <v>97</v>
-      </c>
-      <c r="L43" s="18" t="s">
-        <v>78</v>
-      </c>
-      <c r="M43" s="26" t="s">
-        <v>79</v>
-      </c>
-      <c r="N43" s="17" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="44" spans="1:14" ht="105" x14ac:dyDescent="0.25">
+        <v>117</v>
+      </c>
+      <c r="K43" s="18" t="s">
+        <v>76</v>
+      </c>
+      <c r="L43" s="26" t="s">
+        <v>77</v>
+      </c>
+      <c r="M43" s="17" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="44" spans="1:13" ht="105" x14ac:dyDescent="0.25">
       <c r="A44" s="26">
         <v>43</v>
       </c>
       <c r="B44" s="26" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="C44" s="26" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="D44" s="26" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="E44" s="26" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="F44" s="15">
         <v>45766</v>
@@ -4369,28 +4218,25 @@
         <v>1</v>
       </c>
       <c r="H44" s="25" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="I44" s="15" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="J44" s="25" t="s">
-        <v>124</v>
-      </c>
-      <c r="K44" s="17" t="s">
-        <v>97</v>
-      </c>
-      <c r="L44" s="18" t="s">
-        <v>78</v>
-      </c>
-      <c r="M44" s="26" t="s">
-        <v>79</v>
-      </c>
-      <c r="N44" s="17" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="45" spans="1:14" ht="120" x14ac:dyDescent="0.25">
+        <v>119</v>
+      </c>
+      <c r="K44" s="18" t="s">
+        <v>76</v>
+      </c>
+      <c r="L44" s="26" t="s">
+        <v>77</v>
+      </c>
+      <c r="M44" s="17" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="45" spans="1:13" ht="120" x14ac:dyDescent="0.25">
       <c r="A45" s="26">
         <v>44</v>
       </c>
@@ -4398,13 +4244,13 @@
         <v>27</v>
       </c>
       <c r="C45" s="26" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D45" s="26" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="E45" s="26" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="F45" s="15">
         <v>45767</v>
@@ -4413,42 +4259,39 @@
         <v>1</v>
       </c>
       <c r="H45" s="25" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="I45" s="15" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="J45" s="25" t="s">
-        <v>112</v>
-      </c>
-      <c r="K45" s="17" t="s">
-        <v>77</v>
-      </c>
-      <c r="L45" s="18" t="s">
-        <v>78</v>
-      </c>
-      <c r="M45" s="26" t="s">
-        <v>79</v>
-      </c>
-      <c r="N45" s="17" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="46" spans="1:14" ht="60" x14ac:dyDescent="0.25">
+        <v>107</v>
+      </c>
+      <c r="K45" s="18" t="s">
+        <v>76</v>
+      </c>
+      <c r="L45" s="26" t="s">
+        <v>77</v>
+      </c>
+      <c r="M45" s="17" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="46" spans="1:13" ht="60" x14ac:dyDescent="0.25">
       <c r="A46" s="26">
         <v>45</v>
       </c>
       <c r="B46" s="26" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="C46" s="26" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D46" s="26" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="E46" s="26" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="F46" s="15">
         <v>45770</v>
@@ -4457,28 +4300,25 @@
         <v>1</v>
       </c>
       <c r="H46" s="25" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="I46" s="15" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="J46" s="25" t="s">
-        <v>105</v>
-      </c>
-      <c r="K46" s="17" t="s">
-        <v>97</v>
-      </c>
-      <c r="L46" s="18" t="s">
-        <v>78</v>
-      </c>
-      <c r="M46" s="26" t="s">
-        <v>79</v>
-      </c>
-      <c r="N46" s="17" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="47" spans="1:14" ht="120" x14ac:dyDescent="0.25">
+        <v>100</v>
+      </c>
+      <c r="K46" s="18" t="s">
+        <v>76</v>
+      </c>
+      <c r="L46" s="26" t="s">
+        <v>77</v>
+      </c>
+      <c r="M46" s="17" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="47" spans="1:13" ht="120" x14ac:dyDescent="0.25">
       <c r="A47" s="26">
         <v>46</v>
       </c>
@@ -4486,13 +4326,13 @@
         <v>24</v>
       </c>
       <c r="C47" s="26" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="D47" s="26" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="E47" s="26" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="F47" s="15">
         <v>45773</v>
@@ -4501,42 +4341,39 @@
         <v>1</v>
       </c>
       <c r="H47" s="25" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="I47" s="15" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="J47" s="25" t="s">
-        <v>112</v>
-      </c>
-      <c r="K47" s="17" t="s">
-        <v>77</v>
-      </c>
-      <c r="L47" s="18" t="s">
-        <v>78</v>
-      </c>
-      <c r="M47" s="26" t="s">
-        <v>79</v>
-      </c>
-      <c r="N47" s="17" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="48" spans="1:14" ht="120" x14ac:dyDescent="0.25">
+        <v>107</v>
+      </c>
+      <c r="K47" s="18" t="s">
+        <v>76</v>
+      </c>
+      <c r="L47" s="26" t="s">
+        <v>77</v>
+      </c>
+      <c r="M47" s="17" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="48" spans="1:13" ht="120" x14ac:dyDescent="0.25">
       <c r="A48" s="26">
         <v>47</v>
       </c>
       <c r="B48" s="26" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="C48" s="26" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="D48" s="26" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="E48" s="26" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="F48" s="15">
         <v>45775</v>
@@ -4545,28 +4382,25 @@
         <v>1</v>
       </c>
       <c r="H48" s="25" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="I48" s="15" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="J48" s="25" t="s">
-        <v>112</v>
-      </c>
-      <c r="K48" s="17" t="s">
-        <v>77</v>
-      </c>
-      <c r="L48" s="18" t="s">
-        <v>78</v>
-      </c>
-      <c r="M48" s="26" t="s">
-        <v>79</v>
-      </c>
-      <c r="N48" s="17" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="49" spans="1:14" ht="45" x14ac:dyDescent="0.25">
+        <v>107</v>
+      </c>
+      <c r="K48" s="18" t="s">
+        <v>76</v>
+      </c>
+      <c r="L48" s="26" t="s">
+        <v>77</v>
+      </c>
+      <c r="M48" s="17" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="49" spans="1:13" ht="45" x14ac:dyDescent="0.25">
       <c r="A49" s="26">
         <v>48</v>
       </c>
@@ -4574,13 +4408,13 @@
         <v>24</v>
       </c>
       <c r="C49" s="26" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="D49" s="26" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="E49" s="26" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="F49" s="15">
         <v>45776</v>
@@ -4589,28 +4423,25 @@
         <v>1</v>
       </c>
       <c r="H49" s="25" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="I49" s="15" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="J49" s="17" t="s">
-        <v>106</v>
-      </c>
-      <c r="K49" s="17" t="s">
-        <v>97</v>
-      </c>
-      <c r="L49" s="18" t="s">
-        <v>78</v>
-      </c>
-      <c r="M49" s="26" t="s">
-        <v>79</v>
-      </c>
-      <c r="N49" s="17" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="50" spans="1:14" ht="60" x14ac:dyDescent="0.25">
+        <v>101</v>
+      </c>
+      <c r="K49" s="18" t="s">
+        <v>76</v>
+      </c>
+      <c r="L49" s="26" t="s">
+        <v>77</v>
+      </c>
+      <c r="M49" s="17" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="50" spans="1:13" ht="60" x14ac:dyDescent="0.25">
       <c r="A50" s="26">
         <v>49</v>
       </c>
@@ -4618,13 +4449,13 @@
         <v>27</v>
       </c>
       <c r="C50" s="26" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D50" s="26" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="E50" s="26" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="F50" s="15">
         <v>45776</v>
@@ -4633,28 +4464,25 @@
         <v>1</v>
       </c>
       <c r="H50" s="25" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="I50" s="15" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="J50" s="17" t="s">
-        <v>106</v>
-      </c>
-      <c r="K50" s="17" t="s">
-        <v>97</v>
-      </c>
-      <c r="L50" s="18" t="s">
-        <v>78</v>
-      </c>
-      <c r="M50" s="26" t="s">
-        <v>79</v>
-      </c>
-      <c r="N50" s="17" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="51" spans="1:14" ht="105" x14ac:dyDescent="0.25">
+        <v>101</v>
+      </c>
+      <c r="K50" s="18" t="s">
+        <v>76</v>
+      </c>
+      <c r="L50" s="26" t="s">
+        <v>77</v>
+      </c>
+      <c r="M50" s="17" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="51" spans="1:13" ht="105" x14ac:dyDescent="0.25">
       <c r="A51" s="26">
         <v>50</v>
       </c>
@@ -4662,13 +4490,13 @@
         <v>36</v>
       </c>
       <c r="C51" s="14" t="s">
+        <v>71</v>
+      </c>
+      <c r="D51" s="26" t="s">
         <v>72</v>
       </c>
-      <c r="D51" s="26" t="s">
-        <v>73</v>
-      </c>
       <c r="E51" s="26" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="F51" s="15">
         <v>45777</v>
@@ -4677,28 +4505,25 @@
         <v>2</v>
       </c>
       <c r="H51" s="25" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="I51" s="15" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="J51" s="25" t="s">
-        <v>125</v>
-      </c>
-      <c r="K51" s="17" t="s">
-        <v>97</v>
-      </c>
-      <c r="L51" s="18" t="s">
-        <v>78</v>
-      </c>
-      <c r="M51" s="26" t="s">
-        <v>79</v>
-      </c>
-      <c r="N51" s="17" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="52" spans="1:14" ht="105" x14ac:dyDescent="0.25">
+        <v>120</v>
+      </c>
+      <c r="K51" s="18" t="s">
+        <v>76</v>
+      </c>
+      <c r="L51" s="26" t="s">
+        <v>77</v>
+      </c>
+      <c r="M51" s="17" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="52" spans="1:13" ht="105" x14ac:dyDescent="0.25">
       <c r="A52" s="26">
         <v>51</v>
       </c>
@@ -4706,13 +4531,13 @@
         <v>36</v>
       </c>
       <c r="C52" s="14" t="s">
+        <v>71</v>
+      </c>
+      <c r="D52" s="26" t="s">
         <v>72</v>
       </c>
-      <c r="D52" s="26" t="s">
-        <v>73</v>
-      </c>
       <c r="E52" s="26" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="F52" s="15">
         <v>45777</v>
@@ -4721,28 +4546,25 @@
         <v>2</v>
       </c>
       <c r="H52" s="25" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="I52" s="15" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="J52" s="25" t="s">
-        <v>125</v>
-      </c>
-      <c r="K52" s="17" t="s">
-        <v>97</v>
-      </c>
-      <c r="L52" s="18" t="s">
-        <v>78</v>
-      </c>
-      <c r="M52" s="26" t="s">
-        <v>79</v>
-      </c>
-      <c r="N52" s="17" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="53" spans="1:14" ht="120" x14ac:dyDescent="0.25">
+        <v>120</v>
+      </c>
+      <c r="K52" s="18" t="s">
+        <v>76</v>
+      </c>
+      <c r="L52" s="26" t="s">
+        <v>77</v>
+      </c>
+      <c r="M52" s="17" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="53" spans="1:13" ht="120" x14ac:dyDescent="0.25">
       <c r="A53" s="26">
         <v>52</v>
       </c>
@@ -4750,83 +4572,77 @@
         <v>19</v>
       </c>
       <c r="C53" s="26" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D53" s="26" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E53" s="26" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="F53" s="38">
         <v>45783</v>
       </c>
       <c r="G53" s="17"/>
       <c r="H53" s="25" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="I53" s="15" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="J53" s="25" t="s">
-        <v>113</v>
-      </c>
-      <c r="K53" s="27" t="s">
-        <v>77</v>
-      </c>
-      <c r="L53" s="18" t="s">
-        <v>78</v>
-      </c>
-      <c r="M53" s="26" t="s">
-        <v>79</v>
-      </c>
-      <c r="N53" s="17" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="54" spans="1:14" ht="120" x14ac:dyDescent="0.25">
+        <v>108</v>
+      </c>
+      <c r="K53" s="18" t="s">
+        <v>76</v>
+      </c>
+      <c r="L53" s="26" t="s">
+        <v>77</v>
+      </c>
+      <c r="M53" s="17" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="54" spans="1:13" ht="120" x14ac:dyDescent="0.25">
       <c r="A54" s="26">
         <v>53</v>
       </c>
       <c r="B54" s="23" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="C54" s="26" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D54" s="26" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="E54" s="26" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="F54" s="38">
         <v>45785</v>
       </c>
       <c r="G54" s="17"/>
       <c r="H54" s="25" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="I54" s="15" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="J54" s="25" t="s">
-        <v>112</v>
-      </c>
-      <c r="K54" s="27" t="s">
-        <v>77</v>
-      </c>
-      <c r="L54" s="18" t="s">
-        <v>78</v>
-      </c>
-      <c r="M54" s="26" t="s">
-        <v>79</v>
-      </c>
-      <c r="N54" s="17" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="55" spans="1:14" ht="120" x14ac:dyDescent="0.25">
+        <v>107</v>
+      </c>
+      <c r="K54" s="18" t="s">
+        <v>76</v>
+      </c>
+      <c r="L54" s="26" t="s">
+        <v>77</v>
+      </c>
+      <c r="M54" s="17" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="55" spans="1:13" ht="120" x14ac:dyDescent="0.25">
       <c r="A55" s="26">
         <v>54</v>
       </c>
@@ -4834,41 +4650,38 @@
         <v>24</v>
       </c>
       <c r="C55" s="26" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="D55" s="26" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="E55" s="26" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="F55" s="38">
         <v>45787</v>
       </c>
       <c r="G55" s="17"/>
       <c r="H55" s="25" t="s">
+        <v>74</v>
+      </c>
+      <c r="I55" s="15" t="s">
         <v>75</v>
       </c>
-      <c r="I55" s="15" t="s">
-        <v>76</v>
-      </c>
       <c r="J55" s="25" t="s">
-        <v>112</v>
-      </c>
-      <c r="K55" s="27" t="s">
-        <v>77</v>
-      </c>
-      <c r="L55" s="18" t="s">
-        <v>78</v>
-      </c>
-      <c r="M55" s="26" t="s">
-        <v>79</v>
-      </c>
-      <c r="N55" s="17" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="56" spans="1:14" ht="105" x14ac:dyDescent="0.25">
+        <v>107</v>
+      </c>
+      <c r="K55" s="18" t="s">
+        <v>76</v>
+      </c>
+      <c r="L55" s="26" t="s">
+        <v>77</v>
+      </c>
+      <c r="M55" s="17" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="56" spans="1:13" ht="105" x14ac:dyDescent="0.25">
       <c r="A56" s="26">
         <v>55</v>
       </c>
@@ -4876,83 +4689,77 @@
         <v>19</v>
       </c>
       <c r="C56" s="26" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D56" s="26" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E56" s="26" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="F56" s="38">
         <v>45790</v>
       </c>
       <c r="G56" s="17"/>
       <c r="H56" s="25" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="I56" s="15" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="J56" s="25" t="s">
-        <v>136</v>
-      </c>
-      <c r="K56" s="27" t="s">
-        <v>97</v>
-      </c>
-      <c r="L56" s="18" t="s">
-        <v>78</v>
-      </c>
-      <c r="M56" s="26" t="s">
-        <v>79</v>
-      </c>
-      <c r="N56" s="17" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="57" spans="1:14" ht="120" x14ac:dyDescent="0.25">
+        <v>131</v>
+      </c>
+      <c r="K56" s="18" t="s">
+        <v>76</v>
+      </c>
+      <c r="L56" s="26" t="s">
+        <v>77</v>
+      </c>
+      <c r="M56" s="17" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="57" spans="1:13" ht="120" x14ac:dyDescent="0.25">
       <c r="A57" s="26">
         <v>56</v>
       </c>
       <c r="B57" s="26" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="C57" s="26" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="D57" s="26" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="E57" s="26" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="F57" s="38">
         <v>45794</v>
       </c>
       <c r="G57" s="17"/>
       <c r="H57" s="25" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="I57" s="15" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="J57" s="25" t="s">
-        <v>138</v>
-      </c>
-      <c r="K57" s="27" t="s">
-        <v>97</v>
-      </c>
-      <c r="L57" s="18" t="s">
-        <v>78</v>
-      </c>
-      <c r="M57" s="26" t="s">
-        <v>79</v>
-      </c>
-      <c r="N57" s="17" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="58" spans="1:14" ht="120" x14ac:dyDescent="0.25">
+        <v>133</v>
+      </c>
+      <c r="K57" s="18" t="s">
+        <v>76</v>
+      </c>
+      <c r="L57" s="26" t="s">
+        <v>77</v>
+      </c>
+      <c r="M57" s="17" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="58" spans="1:13" ht="120" x14ac:dyDescent="0.25">
       <c r="A58" s="26">
         <v>57</v>
       </c>
@@ -4960,83 +4767,77 @@
         <v>19</v>
       </c>
       <c r="C58" s="26" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D58" s="26" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E58" s="26" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="F58" s="38">
         <v>45798</v>
       </c>
       <c r="G58" s="17"/>
       <c r="H58" s="25" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="I58" s="15" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="J58" s="25" t="s">
-        <v>112</v>
-      </c>
-      <c r="K58" s="27" t="s">
-        <v>77</v>
-      </c>
-      <c r="L58" s="18" t="s">
-        <v>78</v>
-      </c>
-      <c r="M58" s="26" t="s">
-        <v>79</v>
-      </c>
-      <c r="N58" s="17" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="59" spans="1:14" ht="135" x14ac:dyDescent="0.25">
+        <v>107</v>
+      </c>
+      <c r="K58" s="18" t="s">
+        <v>76</v>
+      </c>
+      <c r="L58" s="26" t="s">
+        <v>77</v>
+      </c>
+      <c r="M58" s="17" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="59" spans="1:13" ht="135" x14ac:dyDescent="0.25">
       <c r="A59" s="26">
         <v>58</v>
       </c>
       <c r="B59" s="23" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="C59" s="26" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="D59" s="26" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="E59" s="26" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="F59" s="38">
         <v>45800</v>
       </c>
       <c r="G59" s="17"/>
       <c r="H59" s="25" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="I59" s="15" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="J59" s="25" t="s">
-        <v>139</v>
-      </c>
-      <c r="K59" s="27" t="s">
-        <v>77</v>
-      </c>
-      <c r="L59" s="18" t="s">
-        <v>78</v>
-      </c>
-      <c r="M59" s="26" t="s">
-        <v>79</v>
-      </c>
-      <c r="N59" s="17" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="60" spans="1:14" ht="135" x14ac:dyDescent="0.25">
+        <v>134</v>
+      </c>
+      <c r="K59" s="18" t="s">
+        <v>76</v>
+      </c>
+      <c r="L59" s="26" t="s">
+        <v>77</v>
+      </c>
+      <c r="M59" s="17" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="60" spans="1:13" ht="135" x14ac:dyDescent="0.25">
       <c r="A60" s="26">
         <v>59</v>
       </c>
@@ -5044,41 +4845,38 @@
         <v>36</v>
       </c>
       <c r="C60" s="24" t="s">
+        <v>71</v>
+      </c>
+      <c r="D60" s="26" t="s">
         <v>72</v>
       </c>
-      <c r="D60" s="26" t="s">
-        <v>73</v>
-      </c>
       <c r="E60" s="26" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="F60" s="38">
         <v>45804</v>
       </c>
       <c r="G60" s="17"/>
       <c r="H60" s="25" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="I60" s="15" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="J60" s="25" t="s">
-        <v>139</v>
-      </c>
-      <c r="K60" s="27" t="s">
-        <v>77</v>
-      </c>
-      <c r="L60" s="18" t="s">
-        <v>78</v>
-      </c>
-      <c r="M60" s="26" t="s">
-        <v>79</v>
-      </c>
-      <c r="N60" s="17" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="61" spans="1:14" ht="120" x14ac:dyDescent="0.25">
+        <v>134</v>
+      </c>
+      <c r="K60" s="18" t="s">
+        <v>76</v>
+      </c>
+      <c r="L60" s="26" t="s">
+        <v>77</v>
+      </c>
+      <c r="M60" s="17" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="61" spans="1:13" ht="120" x14ac:dyDescent="0.25">
       <c r="A61" s="26">
         <v>60</v>
       </c>
@@ -5086,125 +4884,116 @@
         <v>19</v>
       </c>
       <c r="C61" s="26" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D61" s="26" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E61" s="26" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="F61" s="38">
         <v>45806</v>
       </c>
       <c r="G61" s="17"/>
       <c r="H61" s="25" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="I61" s="15" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="J61" s="25" t="s">
-        <v>112</v>
-      </c>
-      <c r="K61" s="27" t="s">
-        <v>77</v>
-      </c>
-      <c r="L61" s="18" t="s">
-        <v>78</v>
-      </c>
-      <c r="M61" s="26" t="s">
-        <v>79</v>
-      </c>
-      <c r="N61" s="17" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="62" spans="1:14" ht="120" x14ac:dyDescent="0.25">
+        <v>107</v>
+      </c>
+      <c r="K61" s="18" t="s">
+        <v>76</v>
+      </c>
+      <c r="L61" s="26" t="s">
+        <v>77</v>
+      </c>
+      <c r="M61" s="17" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="62" spans="1:13" ht="120" x14ac:dyDescent="0.25">
       <c r="A62" s="26">
         <v>61</v>
       </c>
       <c r="B62" s="23" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="C62" s="26" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D62" s="26" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="E62" s="26" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="F62" s="38">
         <v>45807</v>
       </c>
       <c r="G62" s="17"/>
       <c r="H62" s="25" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="I62" s="15" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="J62" s="25" t="s">
-        <v>112</v>
-      </c>
-      <c r="K62" s="27" t="s">
-        <v>77</v>
-      </c>
-      <c r="L62" s="18" t="s">
-        <v>78</v>
-      </c>
-      <c r="M62" s="26" t="s">
-        <v>79</v>
-      </c>
-      <c r="N62" s="17" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="63" spans="1:14" ht="135" x14ac:dyDescent="0.25">
+        <v>107</v>
+      </c>
+      <c r="K62" s="18" t="s">
+        <v>76</v>
+      </c>
+      <c r="L62" s="26" t="s">
+        <v>77</v>
+      </c>
+      <c r="M62" s="17" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="63" spans="1:13" ht="135" x14ac:dyDescent="0.25">
       <c r="A63" s="26">
         <v>62</v>
       </c>
       <c r="B63" s="23" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="C63" s="26" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="D63" s="26" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="E63" s="26" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="F63" s="38">
         <v>45811</v>
       </c>
       <c r="G63" s="17"/>
       <c r="H63" s="25" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="I63" s="15" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="J63" s="25" t="s">
-        <v>139</v>
-      </c>
-      <c r="K63" s="27" t="s">
-        <v>77</v>
-      </c>
-      <c r="L63" s="28" t="s">
-        <v>78</v>
-      </c>
-      <c r="M63" s="26" t="s">
-        <v>79</v>
-      </c>
-      <c r="N63" s="17" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="64" spans="1:14" ht="90" x14ac:dyDescent="0.25">
+        <v>134</v>
+      </c>
+      <c r="K63" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="L63" s="26" t="s">
+        <v>77</v>
+      </c>
+      <c r="M63" s="17" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="64" spans="1:13" ht="90" x14ac:dyDescent="0.25">
       <c r="A64" s="26">
         <v>63</v>
       </c>
@@ -5212,209 +5001,194 @@
         <v>19</v>
       </c>
       <c r="C64" s="26" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D64" s="26" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E64" s="26" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="F64" s="38">
         <v>45814</v>
       </c>
       <c r="G64" s="17"/>
       <c r="H64" s="25" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="I64" s="15" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="J64" s="25" t="s">
-        <v>141</v>
-      </c>
-      <c r="K64" s="27" t="s">
-        <v>97</v>
-      </c>
-      <c r="L64" s="28" t="s">
-        <v>78</v>
-      </c>
-      <c r="M64" s="26" t="s">
-        <v>79</v>
-      </c>
-      <c r="N64" s="17" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="65" spans="1:14" ht="90" x14ac:dyDescent="0.25">
+        <v>136</v>
+      </c>
+      <c r="K64" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="L64" s="26" t="s">
+        <v>77</v>
+      </c>
+      <c r="M64" s="17" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="65" spans="1:13" ht="90" x14ac:dyDescent="0.25">
       <c r="A65" s="26">
         <v>64</v>
       </c>
       <c r="B65" s="23" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="C65" s="26" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D65" s="26" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="E65" s="26" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="F65" s="38">
         <v>45814</v>
       </c>
       <c r="G65" s="17"/>
       <c r="H65" s="25" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="I65" s="15" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="J65" s="25" t="s">
-        <v>141</v>
-      </c>
-      <c r="K65" s="27" t="s">
-        <v>97</v>
-      </c>
-      <c r="L65" s="28" t="s">
-        <v>78</v>
-      </c>
-      <c r="M65" s="26" t="s">
-        <v>79</v>
-      </c>
-      <c r="N65" s="17" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="66" spans="1:14" ht="90" x14ac:dyDescent="0.25">
+        <v>136</v>
+      </c>
+      <c r="K65" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="L65" s="26" t="s">
+        <v>77</v>
+      </c>
+      <c r="M65" s="17" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="66" spans="1:13" ht="90" x14ac:dyDescent="0.25">
       <c r="A66" s="26">
         <v>65</v>
       </c>
       <c r="B66" s="23" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="C66" s="26" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="D66" s="26" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="E66" s="26" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="F66" s="38">
         <v>45814</v>
       </c>
       <c r="G66" s="17"/>
       <c r="H66" s="25" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="I66" s="15" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="J66" s="25" t="s">
-        <v>141</v>
-      </c>
-      <c r="K66" s="27" t="s">
-        <v>97</v>
-      </c>
-      <c r="L66" s="28" t="s">
-        <v>78</v>
-      </c>
-      <c r="M66" s="26" t="s">
-        <v>79</v>
-      </c>
-      <c r="N66" s="17" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="67" spans="1:14" ht="105" x14ac:dyDescent="0.25">
+        <v>136</v>
+      </c>
+      <c r="K66" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="L66" s="26" t="s">
+        <v>77</v>
+      </c>
+      <c r="M66" s="17" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="67" spans="1:13" ht="105" x14ac:dyDescent="0.25">
       <c r="A67" s="26">
         <v>66</v>
       </c>
       <c r="B67" s="26" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="C67" s="26" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="D67" s="26" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="E67" s="26" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="F67" s="38">
         <v>45814</v>
       </c>
       <c r="G67" s="17"/>
       <c r="H67" s="25" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="I67" s="15" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="J67" s="25" t="s">
-        <v>141</v>
-      </c>
-      <c r="K67" s="27" t="s">
-        <v>97</v>
-      </c>
-      <c r="L67" s="28" t="s">
-        <v>78</v>
-      </c>
-      <c r="M67" s="26" t="s">
-        <v>79</v>
-      </c>
-      <c r="N67" s="17" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="68" spans="1:14" ht="105" x14ac:dyDescent="0.25">
+        <v>136</v>
+      </c>
+      <c r="K67" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="L67" s="26" t="s">
+        <v>77</v>
+      </c>
+      <c r="M67" s="17" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="68" spans="1:13" ht="105" x14ac:dyDescent="0.25">
       <c r="A68" s="26">
         <v>67</v>
       </c>
       <c r="B68" s="26" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="C68" s="26" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="D68" s="26" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="E68" s="26" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="F68" s="38">
         <v>45823</v>
       </c>
       <c r="G68" s="17"/>
       <c r="H68" s="25" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="I68" s="15" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="J68" s="25" t="s">
-        <v>123</v>
-      </c>
-      <c r="K68" s="27" t="s">
-        <v>77</v>
-      </c>
-      <c r="L68" s="28" t="s">
-        <v>78</v>
-      </c>
-      <c r="M68" s="26" t="s">
-        <v>79</v>
-      </c>
-      <c r="N68" s="17" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="69" spans="1:14" ht="75" x14ac:dyDescent="0.25">
+        <v>118</v>
+      </c>
+      <c r="K68" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="L68" s="26" t="s">
+        <v>77</v>
+      </c>
+      <c r="M68" s="17" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="69" spans="1:13" ht="75" x14ac:dyDescent="0.25">
       <c r="A69" s="26">
         <v>68</v>
       </c>
@@ -5422,41 +5196,38 @@
         <v>19</v>
       </c>
       <c r="C69" s="26" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D69" s="26" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E69" s="26" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="F69" s="38">
         <v>45824</v>
       </c>
       <c r="G69" s="17"/>
       <c r="H69" s="25" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="I69" s="15" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="J69" s="25" t="s">
-        <v>123</v>
-      </c>
-      <c r="K69" s="27" t="s">
-        <v>77</v>
-      </c>
-      <c r="L69" s="28" t="s">
-        <v>78</v>
-      </c>
-      <c r="M69" s="26" t="s">
-        <v>79</v>
-      </c>
-      <c r="N69" s="17" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="70" spans="1:14" ht="105" x14ac:dyDescent="0.25">
+        <v>118</v>
+      </c>
+      <c r="K69" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="L69" s="26" t="s">
+        <v>77</v>
+      </c>
+      <c r="M69" s="17" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="70" spans="1:13" ht="105" x14ac:dyDescent="0.25">
       <c r="A70" s="26">
         <v>69</v>
       </c>
@@ -5464,83 +5235,77 @@
         <v>33</v>
       </c>
       <c r="C70" s="24" t="s">
+        <v>71</v>
+      </c>
+      <c r="D70" s="26" t="s">
         <v>72</v>
       </c>
-      <c r="D70" s="26" t="s">
-        <v>73</v>
-      </c>
       <c r="E70" s="26" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="F70" s="38">
         <v>45824</v>
       </c>
       <c r="G70" s="17"/>
       <c r="H70" s="25" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="I70" s="15" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="J70" s="25" t="s">
-        <v>142</v>
-      </c>
-      <c r="K70" s="27" t="s">
-        <v>97</v>
-      </c>
-      <c r="L70" s="28" t="s">
-        <v>78</v>
-      </c>
-      <c r="M70" s="26" t="s">
-        <v>79</v>
-      </c>
-      <c r="N70" s="17" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="71" spans="1:14" ht="60" x14ac:dyDescent="0.25">
+        <v>137</v>
+      </c>
+      <c r="K70" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="L70" s="26" t="s">
+        <v>77</v>
+      </c>
+      <c r="M70" s="17" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="71" spans="1:13" ht="60" x14ac:dyDescent="0.25">
       <c r="A71" s="26">
         <v>70</v>
       </c>
       <c r="B71" s="23" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="C71" s="26" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D71" s="26" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="E71" s="26" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="F71" s="38">
         <v>45828</v>
       </c>
       <c r="G71" s="17"/>
       <c r="H71" s="25" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="I71" s="15" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="J71" s="25" t="s">
-        <v>143</v>
-      </c>
-      <c r="K71" s="27" t="s">
-        <v>97</v>
-      </c>
-      <c r="L71" s="28" t="s">
-        <v>78</v>
-      </c>
-      <c r="M71" s="26" t="s">
-        <v>79</v>
-      </c>
-      <c r="N71" s="17" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="72" spans="1:14" ht="75" x14ac:dyDescent="0.25">
+        <v>138</v>
+      </c>
+      <c r="K71" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="L71" s="26" t="s">
+        <v>77</v>
+      </c>
+      <c r="M71" s="17" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="72" spans="1:13" ht="75" x14ac:dyDescent="0.25">
       <c r="A72" s="26">
         <v>71</v>
       </c>
@@ -5548,97 +5313,91 @@
         <v>19</v>
       </c>
       <c r="C72" s="26" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D72" s="26" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E72" s="26" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="F72" s="38">
         <v>45832</v>
       </c>
       <c r="G72" s="17"/>
       <c r="H72" s="25" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="I72" s="15" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="J72" s="25" t="s">
-        <v>123</v>
-      </c>
-      <c r="K72" s="27" t="s">
-        <v>77</v>
-      </c>
-      <c r="L72" s="28" t="s">
-        <v>78</v>
-      </c>
-      <c r="M72" s="26" t="s">
-        <v>79</v>
-      </c>
-      <c r="N72" s="17" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="73" spans="1:14" ht="75" x14ac:dyDescent="0.25">
+        <v>118</v>
+      </c>
+      <c r="K72" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="L72" s="26" t="s">
+        <v>77</v>
+      </c>
+      <c r="M72" s="17" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="73" spans="1:13" ht="75" x14ac:dyDescent="0.25">
       <c r="A73" s="26">
         <v>72</v>
       </c>
       <c r="B73" s="23" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="C73" s="26" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D73" s="26" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="E73" s="26" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="F73" s="38">
         <v>45833</v>
       </c>
       <c r="G73" s="17"/>
       <c r="H73" s="25" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="I73" s="15" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="J73" s="25" t="s">
-        <v>123</v>
-      </c>
-      <c r="K73" s="27" t="s">
-        <v>77</v>
-      </c>
-      <c r="L73" s="28" t="s">
-        <v>78</v>
-      </c>
-      <c r="M73" s="26" t="s">
-        <v>79</v>
-      </c>
-      <c r="N73" s="17" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="74" spans="1:14" ht="105" x14ac:dyDescent="0.25">
+        <v>118</v>
+      </c>
+      <c r="K73" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="L73" s="26" t="s">
+        <v>77</v>
+      </c>
+      <c r="M73" s="17" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="74" spans="1:13" ht="105" x14ac:dyDescent="0.25">
       <c r="A74" s="26">
         <v>73</v>
       </c>
       <c r="B74" s="27" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="C74" s="26" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="D74" s="26" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="E74" s="26" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="F74" s="38">
         <v>45839</v>
@@ -5647,42 +5406,39 @@
         <v>1</v>
       </c>
       <c r="H74" s="25" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="I74" s="15" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="J74" s="25" t="s">
+        <v>137</v>
+      </c>
+      <c r="K74" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="L74" s="26" t="s">
+        <v>77</v>
+      </c>
+      <c r="M74" s="17" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="75" spans="1:13" ht="75" x14ac:dyDescent="0.25">
+      <c r="A75" s="26">
+        <v>74</v>
+      </c>
+      <c r="B75" s="23" t="s">
         <v>142</v>
       </c>
-      <c r="K74" s="27" t="s">
-        <v>97</v>
-      </c>
-      <c r="L74" s="28" t="s">
-        <v>78</v>
-      </c>
-      <c r="M74" s="26" t="s">
-        <v>79</v>
-      </c>
-      <c r="N74" s="17" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="75" spans="1:14" ht="75" x14ac:dyDescent="0.25">
-      <c r="A75" s="26">
-        <v>74</v>
-      </c>
-      <c r="B75" s="23" t="s">
-        <v>147</v>
-      </c>
       <c r="C75" s="26" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D75" s="26" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E75" s="26" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="F75" s="38">
         <v>45846</v>
@@ -5691,42 +5447,39 @@
         <v>1</v>
       </c>
       <c r="H75" s="25" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="I75" s="15" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="J75" s="25" t="s">
-        <v>123</v>
-      </c>
-      <c r="K75" s="27" t="s">
-        <v>77</v>
-      </c>
-      <c r="L75" s="28" t="s">
-        <v>78</v>
-      </c>
-      <c r="M75" s="26" t="s">
-        <v>79</v>
-      </c>
-      <c r="N75" s="17" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="76" spans="1:14" ht="75" x14ac:dyDescent="0.25">
+        <v>118</v>
+      </c>
+      <c r="K75" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="L75" s="26" t="s">
+        <v>77</v>
+      </c>
+      <c r="M75" s="17" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="76" spans="1:13" ht="75" x14ac:dyDescent="0.25">
       <c r="A76" s="26">
         <v>75</v>
       </c>
       <c r="B76" s="23" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="C76" s="26" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D76" s="23" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="E76" s="26" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="F76" s="38">
         <v>45848</v>
@@ -5735,42 +5488,39 @@
         <v>1</v>
       </c>
       <c r="H76" s="25" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="I76" s="15" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="J76" s="25" t="s">
-        <v>123</v>
-      </c>
-      <c r="K76" s="27" t="s">
-        <v>97</v>
-      </c>
-      <c r="L76" s="28" t="s">
-        <v>78</v>
-      </c>
-      <c r="M76" s="26" t="s">
-        <v>79</v>
-      </c>
-      <c r="N76" s="17" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="77" spans="1:14" ht="105" x14ac:dyDescent="0.25">
+        <v>118</v>
+      </c>
+      <c r="K76" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="L76" s="26" t="s">
+        <v>77</v>
+      </c>
+      <c r="M76" s="17" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="77" spans="1:13" ht="105" x14ac:dyDescent="0.25">
       <c r="A77" s="26">
         <v>76</v>
       </c>
       <c r="B77" s="23" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="C77" s="26" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D77" s="26" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E77" s="26" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="F77" s="38">
         <v>45855</v>
@@ -5779,42 +5529,39 @@
         <v>1</v>
       </c>
       <c r="H77" s="25" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="I77" s="15" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="J77" s="25" t="s">
-        <v>142</v>
-      </c>
-      <c r="K77" s="27" t="s">
-        <v>97</v>
-      </c>
-      <c r="L77" s="28" t="s">
-        <v>78</v>
-      </c>
-      <c r="M77" s="26" t="s">
-        <v>79</v>
-      </c>
-      <c r="N77" s="17" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="78" spans="1:14" ht="60" x14ac:dyDescent="0.25">
+        <v>137</v>
+      </c>
+      <c r="K77" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="L77" s="26" t="s">
+        <v>77</v>
+      </c>
+      <c r="M77" s="17" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="78" spans="1:13" ht="60" x14ac:dyDescent="0.25">
       <c r="A78" s="26">
         <v>77</v>
       </c>
       <c r="B78" s="27" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="C78" s="26" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="D78" s="26" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="E78" s="26" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="F78" s="38">
         <v>45858</v>
@@ -5823,42 +5570,39 @@
         <v>1</v>
       </c>
       <c r="H78" s="25" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="I78" s="15" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="J78" s="25" t="s">
-        <v>143</v>
-      </c>
-      <c r="K78" s="27" t="s">
-        <v>77</v>
-      </c>
-      <c r="L78" s="28" t="s">
-        <v>78</v>
-      </c>
-      <c r="M78" s="26" t="s">
-        <v>79</v>
-      </c>
-      <c r="N78" s="17" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="79" spans="1:14" ht="105" x14ac:dyDescent="0.25">
+        <v>138</v>
+      </c>
+      <c r="K78" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="L78" s="26" t="s">
+        <v>77</v>
+      </c>
+      <c r="M78" s="17" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="79" spans="1:13" ht="105" x14ac:dyDescent="0.25">
       <c r="A79" s="26">
         <v>78</v>
       </c>
       <c r="B79" s="26" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="C79" s="26" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D79" s="26" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="E79" s="26" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="F79" s="38">
         <v>45859</v>
@@ -5867,42 +5611,39 @@
         <v>1</v>
       </c>
       <c r="H79" s="25" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="I79" s="15" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="J79" s="25" t="s">
-        <v>142</v>
-      </c>
-      <c r="K79" s="27" t="s">
-        <v>77</v>
-      </c>
-      <c r="L79" s="28" t="s">
-        <v>78</v>
-      </c>
-      <c r="M79" s="26" t="s">
-        <v>79</v>
-      </c>
-      <c r="N79" s="17" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="80" spans="1:14" ht="105" x14ac:dyDescent="0.25">
+        <v>137</v>
+      </c>
+      <c r="K79" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="L79" s="26" t="s">
+        <v>77</v>
+      </c>
+      <c r="M79" s="17" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="80" spans="1:13" ht="105" x14ac:dyDescent="0.25">
       <c r="A80" s="26">
         <v>79</v>
       </c>
       <c r="B80" s="26" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="C80" s="26" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="D80" s="26" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="E80" s="26" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="F80" s="38">
         <v>45861</v>
@@ -5911,42 +5652,39 @@
         <v>1</v>
       </c>
       <c r="H80" s="25" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="I80" s="15" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="J80" s="25" t="s">
-        <v>142</v>
-      </c>
-      <c r="K80" s="27" t="s">
-        <v>97</v>
-      </c>
-      <c r="L80" s="28" t="s">
-        <v>78</v>
-      </c>
-      <c r="M80" s="26" t="s">
-        <v>79</v>
-      </c>
-      <c r="N80" s="17" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="81" spans="1:14" ht="105" x14ac:dyDescent="0.25">
+        <v>137</v>
+      </c>
+      <c r="K80" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="L80" s="26" t="s">
+        <v>77</v>
+      </c>
+      <c r="M80" s="17" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="81" spans="1:13" ht="105" x14ac:dyDescent="0.25">
       <c r="A81" s="26">
         <v>80</v>
       </c>
       <c r="B81" s="26" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="C81" s="26" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D81" s="26" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="E81" s="26" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="F81" s="38">
         <v>45868</v>
@@ -5955,42 +5693,39 @@
         <v>1</v>
       </c>
       <c r="H81" s="25" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="I81" s="15" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="J81" s="25" t="s">
-        <v>142</v>
-      </c>
-      <c r="K81" s="27" t="s">
-        <v>77</v>
-      </c>
-      <c r="L81" s="28" t="s">
-        <v>78</v>
-      </c>
-      <c r="M81" s="26" t="s">
-        <v>79</v>
-      </c>
-      <c r="N81" s="17" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="82" spans="1:14" ht="90" x14ac:dyDescent="0.25">
+        <v>137</v>
+      </c>
+      <c r="K81" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="L81" s="26" t="s">
+        <v>77</v>
+      </c>
+      <c r="M81" s="17" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="82" spans="1:13" ht="90" x14ac:dyDescent="0.25">
       <c r="A82" s="26">
         <v>81</v>
       </c>
       <c r="B82" s="27" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="C82" s="26" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="D82" s="26" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="E82" s="26" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="F82" s="38">
         <v>45868</v>
@@ -5999,42 +5734,39 @@
         <v>1</v>
       </c>
       <c r="H82" s="25" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="I82" s="15" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="J82" s="25" t="s">
-        <v>141</v>
-      </c>
-      <c r="K82" s="27" t="s">
-        <v>97</v>
-      </c>
-      <c r="L82" s="28" t="s">
-        <v>78</v>
-      </c>
-      <c r="M82" s="26" t="s">
-        <v>79</v>
-      </c>
-      <c r="N82" s="17" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="83" spans="1:14" ht="90" x14ac:dyDescent="0.25">
+        <v>136</v>
+      </c>
+      <c r="K82" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="L82" s="26" t="s">
+        <v>77</v>
+      </c>
+      <c r="M82" s="17" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="83" spans="1:13" ht="90" x14ac:dyDescent="0.25">
       <c r="A83" s="26">
         <v>82</v>
       </c>
       <c r="B83" s="27" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="C83" s="26" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="D83" s="26" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="E83" s="26" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="F83" s="38">
         <v>45870</v>
@@ -6043,42 +5775,39 @@
         <v>1</v>
       </c>
       <c r="H83" s="25" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="I83" s="15" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="J83" s="25" t="s">
-        <v>141</v>
-      </c>
-      <c r="K83" s="27" t="s">
-        <v>97</v>
-      </c>
-      <c r="L83" s="28" t="s">
-        <v>78</v>
-      </c>
-      <c r="M83" s="26" t="s">
-        <v>79</v>
-      </c>
-      <c r="N83" s="17" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="84" spans="1:14" ht="90" x14ac:dyDescent="0.25">
+        <v>136</v>
+      </c>
+      <c r="K83" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="L83" s="26" t="s">
+        <v>77</v>
+      </c>
+      <c r="M83" s="17" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="84" spans="1:13" ht="90" x14ac:dyDescent="0.25">
       <c r="A84" s="26">
         <v>83</v>
       </c>
       <c r="B84" s="26" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="C84" s="26" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D84" s="26" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="E84" s="26" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="F84" s="38">
         <v>45870</v>
@@ -6087,42 +5816,39 @@
         <v>1</v>
       </c>
       <c r="H84" s="25" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="I84" s="15" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="J84" s="25" t="s">
-        <v>141</v>
-      </c>
-      <c r="K84" s="27" t="s">
-        <v>97</v>
-      </c>
-      <c r="L84" s="28" t="s">
-        <v>78</v>
-      </c>
-      <c r="M84" s="26" t="s">
-        <v>79</v>
-      </c>
-      <c r="N84" s="17" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="85" spans="1:14" ht="75" x14ac:dyDescent="0.25">
+        <v>136</v>
+      </c>
+      <c r="K84" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="L84" s="26" t="s">
+        <v>77</v>
+      </c>
+      <c r="M84" s="17" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="85" spans="1:13" ht="75" x14ac:dyDescent="0.25">
       <c r="A85" s="26">
         <v>84</v>
       </c>
       <c r="B85" s="23" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="C85" s="26" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D85" s="26" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E85" s="26" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="F85" s="38">
         <v>45878</v>
@@ -6131,42 +5857,39 @@
         <v>1</v>
       </c>
       <c r="H85" s="25" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="I85" s="15" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="J85" s="25" t="s">
-        <v>123</v>
-      </c>
-      <c r="K85" s="27" t="s">
-        <v>77</v>
-      </c>
-      <c r="L85" s="28" t="s">
-        <v>78</v>
-      </c>
-      <c r="M85" s="26" t="s">
-        <v>79</v>
-      </c>
-      <c r="N85" s="17" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="86" spans="1:14" ht="75" x14ac:dyDescent="0.25">
+        <v>118</v>
+      </c>
+      <c r="K85" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="L85" s="26" t="s">
+        <v>77</v>
+      </c>
+      <c r="M85" s="17" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="86" spans="1:13" ht="75" x14ac:dyDescent="0.25">
       <c r="A86" s="26">
         <v>85</v>
       </c>
       <c r="B86" s="23" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="C86" s="26" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D86" s="23" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="E86" s="26" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="F86" s="38">
         <v>45889</v>
@@ -6175,42 +5898,39 @@
         <v>1</v>
       </c>
       <c r="H86" s="25" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="I86" s="15" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="J86" s="25" t="s">
-        <v>123</v>
-      </c>
-      <c r="K86" s="27" t="s">
-        <v>97</v>
-      </c>
-      <c r="L86" s="28" t="s">
-        <v>78</v>
-      </c>
-      <c r="M86" s="26" t="s">
-        <v>79</v>
-      </c>
-      <c r="N86" s="17" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="87" spans="1:14" ht="90" x14ac:dyDescent="0.25">
+        <v>118</v>
+      </c>
+      <c r="K86" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="L86" s="26" t="s">
+        <v>77</v>
+      </c>
+      <c r="M86" s="17" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="87" spans="1:13" ht="90" x14ac:dyDescent="0.25">
       <c r="A87" s="26">
         <v>86</v>
       </c>
       <c r="B87" s="23" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="C87" s="26" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="D87" s="26" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="E87" s="26" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="F87" s="38">
         <v>45895</v>
@@ -6219,42 +5939,39 @@
         <v>1</v>
       </c>
       <c r="H87" s="25" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="I87" s="15" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="J87" s="25" t="s">
-        <v>158</v>
-      </c>
-      <c r="K87" s="27" t="s">
-        <v>97</v>
-      </c>
-      <c r="L87" s="28" t="s">
-        <v>78</v>
-      </c>
-      <c r="M87" s="26" t="s">
-        <v>79</v>
-      </c>
-      <c r="N87" s="17" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="88" spans="1:14" ht="105" x14ac:dyDescent="0.25">
+        <v>153</v>
+      </c>
+      <c r="K87" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="L87" s="26" t="s">
+        <v>77</v>
+      </c>
+      <c r="M87" s="17" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="88" spans="1:13" ht="105" x14ac:dyDescent="0.25">
       <c r="A88" s="26">
         <v>87</v>
       </c>
       <c r="B88" s="26" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="C88" s="26" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="D88" s="26" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="E88" s="26" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="F88" s="38">
         <v>45895</v>
@@ -6263,42 +5980,39 @@
         <v>1</v>
       </c>
       <c r="H88" s="25" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="I88" s="15" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="J88" s="25" t="s">
-        <v>123</v>
-      </c>
-      <c r="K88" s="27" t="s">
-        <v>77</v>
-      </c>
-      <c r="L88" s="28" t="s">
-        <v>78</v>
-      </c>
-      <c r="M88" s="26" t="s">
-        <v>79</v>
-      </c>
-      <c r="N88" s="17" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="89" spans="1:14" ht="105" x14ac:dyDescent="0.25">
+        <v>118</v>
+      </c>
+      <c r="K88" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="L88" s="26" t="s">
+        <v>77</v>
+      </c>
+      <c r="M88" s="17" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="89" spans="1:13" ht="105" x14ac:dyDescent="0.25">
       <c r="A89" s="26">
         <v>88</v>
       </c>
       <c r="B89" s="26" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="C89" s="26" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="D89" s="26" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="E89" s="26" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="F89" s="38">
         <v>45897</v>
@@ -6307,42 +6021,39 @@
         <v>1</v>
       </c>
       <c r="H89" s="25" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="I89" s="15" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="J89" s="25" t="s">
-        <v>123</v>
-      </c>
-      <c r="K89" s="27" t="s">
-        <v>77</v>
-      </c>
-      <c r="L89" s="28" t="s">
-        <v>78</v>
-      </c>
-      <c r="M89" s="26" t="s">
-        <v>79</v>
-      </c>
-      <c r="N89" s="17" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="90" spans="1:14" ht="120" x14ac:dyDescent="0.25">
+        <v>118</v>
+      </c>
+      <c r="K89" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="L89" s="26" t="s">
+        <v>77</v>
+      </c>
+      <c r="M89" s="17" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="90" spans="1:13" ht="120" x14ac:dyDescent="0.25">
       <c r="A90" s="26">
         <v>89</v>
       </c>
       <c r="B90" s="27" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="C90" s="26" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="D90" s="26" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="E90" s="26" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="F90" s="38">
         <v>45944</v>
@@ -6351,42 +6062,39 @@
         <v>1</v>
       </c>
       <c r="H90" s="25" t="s">
+        <v>74</v>
+      </c>
+      <c r="I90" s="15" t="s">
         <v>75</v>
       </c>
-      <c r="I90" s="15" t="s">
-        <v>76</v>
-      </c>
       <c r="J90" s="25" t="s">
-        <v>112</v>
-      </c>
-      <c r="K90" s="27" t="s">
-        <v>77</v>
-      </c>
-      <c r="L90" s="28" t="s">
-        <v>78</v>
-      </c>
-      <c r="M90" s="26" t="s">
-        <v>79</v>
-      </c>
-      <c r="N90" s="17" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="91" spans="1:14" ht="75" x14ac:dyDescent="0.25">
+        <v>107</v>
+      </c>
+      <c r="K90" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="L90" s="26" t="s">
+        <v>77</v>
+      </c>
+      <c r="M90" s="17" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="91" spans="1:13" ht="75" x14ac:dyDescent="0.25">
       <c r="A91" s="26">
         <v>90</v>
       </c>
       <c r="B91" s="23" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="C91" s="26" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D91" s="23" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="E91" s="26" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="F91" s="38">
         <v>45947</v>
@@ -6395,42 +6103,39 @@
         <v>1</v>
       </c>
       <c r="H91" s="25" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="I91" s="15" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="J91" s="25" t="s">
-        <v>123</v>
-      </c>
-      <c r="K91" s="27" t="s">
-        <v>77</v>
-      </c>
-      <c r="L91" s="28" t="s">
-        <v>78</v>
-      </c>
-      <c r="M91" s="26" t="s">
-        <v>79</v>
-      </c>
-      <c r="N91" s="17" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="92" spans="1:14" ht="150" x14ac:dyDescent="0.25">
+        <v>118</v>
+      </c>
+      <c r="K91" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="L91" s="26" t="s">
+        <v>77</v>
+      </c>
+      <c r="M91" s="17" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="92" spans="1:13" ht="150" x14ac:dyDescent="0.25">
       <c r="A92" s="26">
         <v>91</v>
       </c>
       <c r="B92" s="23" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="C92" s="26" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D92" s="23" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="E92" s="26" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="F92" s="38">
         <v>45948</v>
@@ -6439,42 +6144,39 @@
         <v>1</v>
       </c>
       <c r="H92" s="25" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="I92" s="15" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="J92" s="25" t="s">
-        <v>162</v>
-      </c>
-      <c r="K92" s="27" t="s">
-        <v>97</v>
-      </c>
-      <c r="L92" s="28" t="s">
-        <v>78</v>
-      </c>
-      <c r="M92" s="26" t="s">
-        <v>79</v>
-      </c>
-      <c r="N92" s="17" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="93" spans="1:14" ht="75" x14ac:dyDescent="0.25">
+        <v>157</v>
+      </c>
+      <c r="K92" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="L92" s="26" t="s">
+        <v>77</v>
+      </c>
+      <c r="M92" s="17" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="93" spans="1:13" ht="75" x14ac:dyDescent="0.25">
       <c r="A93" s="26">
         <v>92</v>
       </c>
       <c r="B93" s="23" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="C93" s="26" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D93" s="23" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="E93" s="26" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="F93" s="38">
         <v>45954</v>
@@ -6483,42 +6185,39 @@
         <v>1</v>
       </c>
       <c r="H93" s="25" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="I93" s="15" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="J93" s="25" t="s">
-        <v>123</v>
-      </c>
-      <c r="K93" s="27" t="s">
-        <v>77</v>
-      </c>
-      <c r="L93" s="28" t="s">
-        <v>78</v>
-      </c>
-      <c r="M93" s="26" t="s">
-        <v>79</v>
-      </c>
-      <c r="N93" s="17" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="94" spans="1:14" ht="75" x14ac:dyDescent="0.25">
+        <v>118</v>
+      </c>
+      <c r="K93" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="L93" s="26" t="s">
+        <v>77</v>
+      </c>
+      <c r="M93" s="17" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="94" spans="1:13" ht="75" x14ac:dyDescent="0.25">
       <c r="A94" s="26">
         <v>93</v>
       </c>
       <c r="B94" s="23" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="C94" s="26" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D94" s="23" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="E94" s="26" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="F94" s="38">
         <v>45955</v>
@@ -6527,25 +6226,22 @@
         <v>1</v>
       </c>
       <c r="H94" s="25" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="I94" s="15" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="J94" s="25" t="s">
-        <v>123</v>
-      </c>
-      <c r="K94" s="27" t="s">
-        <v>77</v>
-      </c>
-      <c r="L94" s="28" t="s">
-        <v>78</v>
-      </c>
-      <c r="M94" s="26" t="s">
-        <v>79</v>
-      </c>
-      <c r="N94" s="17" t="s">
-        <v>80</v>
+        <v>118</v>
+      </c>
+      <c r="K94" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="L94" s="26" t="s">
+        <v>77</v>
+      </c>
+      <c r="M94" s="17" t="s">
+        <v>78</v>
       </c>
     </row>
   </sheetData>
@@ -6556,7 +6252,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L64"/>
+  <dimension ref="A1:K64"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.42578125" style="52" bestFit="1" customWidth="1"/>
@@ -6568,15 +6264,14 @@
     <col min="7" max="7" width="21.85546875" style="52" customWidth="1"/>
     <col min="8" max="8" width="25.28515625" style="52" customWidth="1"/>
     <col min="9" max="9" width="99.7109375" style="52" customWidth="1"/>
-    <col min="10" max="10" width="20" style="52" customWidth="1"/>
-    <col min="11" max="11" width="22.7109375" style="52" customWidth="1"/>
-    <col min="12" max="12" width="11.5703125" style="52" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="11.42578125" style="52"/>
-    <col min="14" max="14" width="11.5703125" style="52" bestFit="1" customWidth="1"/>
-    <col min="15" max="16384" width="11.42578125" style="52"/>
+    <col min="10" max="10" width="22.7109375" style="52" customWidth="1"/>
+    <col min="11" max="11" width="11.5703125" style="52" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="11.42578125" style="52"/>
+    <col min="13" max="13" width="11.5703125" style="52" bestFit="1" customWidth="1"/>
+    <col min="14" max="16384" width="11.42578125" style="52"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
         <v>59</v>
       </c>
@@ -6608,2403 +6303,2211 @@
         <v>68</v>
       </c>
       <c r="K1" s="11" t="s">
-        <v>69</v>
-      </c>
-      <c r="L1" s="11" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" ht="60" x14ac:dyDescent="0.25">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A2" s="23">
         <v>1</v>
       </c>
       <c r="B2" s="23" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="C2" s="23" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="D2" s="26" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E2" s="23" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F2" s="53">
         <v>46025</v>
       </c>
       <c r="G2" s="25" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="H2" s="54" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="I2" s="25" t="s">
-        <v>165</v>
-      </c>
-      <c r="J2" s="55" t="s">
-        <v>97</v>
-      </c>
-      <c r="K2" s="28" t="s">
-        <v>78</v>
-      </c>
-      <c r="L2" s="39">
+        <v>160</v>
+      </c>
+      <c r="J2" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="K2" s="39">
         <v>50</v>
       </c>
     </row>
-    <row r="3" spans="1:12" ht="75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" ht="75" x14ac:dyDescent="0.25">
       <c r="A3" s="23">
         <v>2</v>
       </c>
       <c r="B3" s="23" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="C3" s="23" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="D3" s="26" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E3" s="23" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F3" s="53">
         <v>46030</v>
       </c>
       <c r="G3" s="25" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="H3" s="54" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="I3" s="25" t="s">
-        <v>166</v>
-      </c>
-      <c r="J3" s="55" t="s">
-        <v>97</v>
-      </c>
-      <c r="K3" s="28" t="s">
-        <v>78</v>
-      </c>
-      <c r="L3" s="39">
+        <v>161</v>
+      </c>
+      <c r="J3" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="K3" s="39">
         <v>50</v>
       </c>
     </row>
-    <row r="4" spans="1:12" ht="75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" ht="75" x14ac:dyDescent="0.25">
       <c r="A4" s="23">
         <v>3</v>
       </c>
       <c r="B4" s="23" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="C4" s="23" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="D4" s="26" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="E4" s="26" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F4" s="53">
         <v>46030</v>
       </c>
       <c r="G4" s="25" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H4" s="54" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="I4" s="25" t="s">
-        <v>167</v>
-      </c>
-      <c r="J4" s="55" t="s">
-        <v>97</v>
-      </c>
-      <c r="K4" s="28" t="s">
-        <v>78</v>
-      </c>
-      <c r="L4" s="39">
+        <v>162</v>
+      </c>
+      <c r="J4" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="K4" s="39">
         <v>50</v>
       </c>
     </row>
-    <row r="5" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A5" s="23">
         <v>4</v>
       </c>
       <c r="B5" s="23" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="C5" s="23" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="D5" s="26" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="E5" s="26" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F5" s="53">
         <v>46032</v>
       </c>
       <c r="G5" s="25" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H5" s="54" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="I5" s="25" t="s">
-        <v>168</v>
-      </c>
-      <c r="J5" s="55" t="s">
-        <v>97</v>
-      </c>
-      <c r="K5" s="28" t="s">
-        <v>78</v>
-      </c>
-      <c r="L5" s="39">
+        <v>163</v>
+      </c>
+      <c r="J5" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="K5" s="39">
         <v>50</v>
       </c>
     </row>
-    <row r="6" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A6" s="23">
         <v>5</v>
       </c>
       <c r="B6" s="23" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="C6" s="23" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="D6" s="26" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="E6" s="26" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F6" s="53">
         <v>46034</v>
       </c>
       <c r="G6" s="25" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H6" s="54" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="I6" s="25" t="s">
-        <v>171</v>
-      </c>
-      <c r="J6" s="55" t="s">
-        <v>97</v>
-      </c>
-      <c r="K6" s="28" t="s">
-        <v>78</v>
-      </c>
-      <c r="L6" s="39">
+        <v>166</v>
+      </c>
+      <c r="J6" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="K6" s="39">
         <v>50</v>
       </c>
     </row>
-    <row r="7" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A7" s="23">
         <v>6</v>
       </c>
       <c r="B7" s="23" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="C7" s="23" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="D7" s="26" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="E7" s="26" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F7" s="53">
         <v>46035</v>
       </c>
       <c r="G7" s="25" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H7" s="54" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="I7" s="25" t="s">
-        <v>175</v>
-      </c>
-      <c r="J7" s="55" t="s">
-        <v>92</v>
-      </c>
-      <c r="K7" s="28" t="s">
-        <v>78</v>
-      </c>
-      <c r="L7" s="56">
+        <v>170</v>
+      </c>
+      <c r="J7" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="K7" s="56">
         <v>73.75</v>
       </c>
     </row>
-    <row r="8" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A8" s="23">
         <v>7</v>
       </c>
       <c r="B8" s="23" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="C8" s="23" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="D8" s="26" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="E8" s="26" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F8" s="53">
         <v>46037</v>
       </c>
       <c r="G8" s="25" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H8" s="54" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="I8" s="25" t="s">
-        <v>168</v>
-      </c>
-      <c r="J8" s="55" t="s">
-        <v>97</v>
-      </c>
-      <c r="K8" s="28" t="s">
-        <v>78</v>
-      </c>
-      <c r="L8" s="39">
+        <v>163</v>
+      </c>
+      <c r="J8" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="K8" s="39">
         <v>50</v>
       </c>
     </row>
-    <row r="9" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A9" s="23">
         <v>8</v>
       </c>
       <c r="B9" s="23" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="C9" s="23" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="D9" s="26" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="E9" s="26" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F9" s="53">
         <v>46042</v>
       </c>
       <c r="G9" s="25" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H9" s="54" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="I9" s="25" t="s">
-        <v>168</v>
-      </c>
-      <c r="J9" s="55" t="s">
-        <v>97</v>
-      </c>
-      <c r="K9" s="28" t="s">
-        <v>78</v>
-      </c>
-      <c r="L9" s="39">
+        <v>163</v>
+      </c>
+      <c r="J9" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="K9" s="39">
         <v>50</v>
       </c>
     </row>
-    <row r="10" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A10" s="23">
         <v>9</v>
       </c>
       <c r="B10" s="23" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="C10" s="23" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="D10" s="26" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="E10" s="26" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F10" s="53">
         <v>46042</v>
       </c>
       <c r="G10" s="25" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H10" s="54" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="I10" s="25" t="s">
-        <v>177</v>
-      </c>
-      <c r="J10" s="55" t="s">
-        <v>77</v>
-      </c>
-      <c r="K10" s="28" t="s">
-        <v>78</v>
-      </c>
-      <c r="L10" s="39">
+        <v>172</v>
+      </c>
+      <c r="J10" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="K10" s="39">
         <v>37.5</v>
       </c>
     </row>
-    <row r="11" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A11" s="23">
         <v>10</v>
       </c>
       <c r="B11" s="23" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="C11" s="23" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="D11" s="26" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="E11" s="26" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F11" s="53">
         <v>46044</v>
       </c>
       <c r="G11" s="25" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H11" s="54" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="I11" s="25" t="s">
-        <v>168</v>
-      </c>
-      <c r="J11" s="55" t="s">
-        <v>97</v>
-      </c>
-      <c r="K11" s="28" t="s">
-        <v>78</v>
-      </c>
-      <c r="L11" s="39">
+        <v>163</v>
+      </c>
+      <c r="J11" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="K11" s="39">
         <v>50</v>
       </c>
     </row>
-    <row r="12" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A12" s="23">
         <v>11</v>
       </c>
       <c r="B12" s="23" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="C12" s="23" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="D12" s="26" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="E12" s="26" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F12" s="53">
         <v>46048</v>
       </c>
       <c r="G12" s="25" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H12" s="54" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="I12" s="25" t="s">
-        <v>179</v>
-      </c>
-      <c r="J12" s="55" t="s">
-        <v>92</v>
-      </c>
-      <c r="K12" s="28" t="s">
-        <v>78</v>
-      </c>
-      <c r="L12" s="56">
+        <v>174</v>
+      </c>
+      <c r="J12" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="K12" s="56">
         <v>73.75</v>
       </c>
     </row>
-    <row r="13" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A13" s="23">
         <v>12</v>
       </c>
       <c r="B13" s="23" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="C13" s="55" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="D13" s="26" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="E13" s="26" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F13" s="53">
         <v>46048</v>
       </c>
       <c r="G13" s="25" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H13" s="54" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="I13" s="25" t="s">
-        <v>180</v>
-      </c>
-      <c r="J13" s="55" t="s">
-        <v>92</v>
-      </c>
-      <c r="K13" s="28" t="s">
-        <v>78</v>
-      </c>
-      <c r="L13" s="56">
+        <v>175</v>
+      </c>
+      <c r="J13" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="K13" s="56">
         <v>73.75</v>
       </c>
     </row>
-    <row r="14" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A14" s="23">
         <v>13</v>
       </c>
       <c r="B14" s="23" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="C14" s="26" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="D14" s="26" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="E14" s="26" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="F14" s="53">
         <v>46065</v>
       </c>
       <c r="G14" s="25" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H14" s="54" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="I14" s="25" t="s">
-        <v>182</v>
-      </c>
-      <c r="J14" s="55" t="s">
-        <v>97</v>
-      </c>
-      <c r="K14" s="28" t="s">
-        <v>78</v>
-      </c>
-      <c r="L14" s="39">
+        <v>177</v>
+      </c>
+      <c r="J14" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="K14" s="39">
         <v>50</v>
       </c>
     </row>
-    <row r="15" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A15" s="23">
         <v>14</v>
       </c>
       <c r="B15" s="23" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="C15" s="23" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="D15" s="26" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="E15" s="26" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="F15" s="53">
         <v>46065</v>
       </c>
       <c r="G15" s="25" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="H15" s="40" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="I15" s="25" t="s">
-        <v>183</v>
-      </c>
-      <c r="J15" s="55" t="s">
-        <v>97</v>
-      </c>
-      <c r="K15" s="28" t="s">
-        <v>78</v>
-      </c>
-      <c r="L15" s="39">
+        <v>178</v>
+      </c>
+      <c r="J15" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="K15" s="39">
         <v>50</v>
       </c>
     </row>
-    <row r="16" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A16" s="23">
         <v>15</v>
       </c>
       <c r="B16" s="23" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="C16" s="23" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="D16" s="26" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E16" s="23" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="F16" s="53">
         <v>46068</v>
       </c>
       <c r="G16" s="25" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="H16" s="54" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="I16" s="25" t="s">
-        <v>123</v>
-      </c>
-      <c r="J16" s="55" t="s">
-        <v>77</v>
-      </c>
-      <c r="K16" s="28" t="s">
-        <v>78</v>
-      </c>
-      <c r="L16" s="39">
+        <v>118</v>
+      </c>
+      <c r="J16" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="K16" s="39">
         <v>37.5</v>
       </c>
     </row>
-    <row r="17" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A17" s="23">
         <v>16</v>
       </c>
       <c r="B17" s="23" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="C17" s="26" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="D17" s="26" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="E17" s="26" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="F17" s="53">
         <v>46068</v>
       </c>
       <c r="G17" s="25" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="H17" s="54" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="I17" s="25" t="s">
-        <v>123</v>
-      </c>
-      <c r="J17" s="55" t="s">
-        <v>77</v>
-      </c>
-      <c r="K17" s="28" t="s">
-        <v>78</v>
-      </c>
-      <c r="L17" s="39">
+        <v>118</v>
+      </c>
+      <c r="J17" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="K17" s="39">
         <v>37.5</v>
       </c>
     </row>
-    <row r="18" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A18" s="23">
         <v>17</v>
       </c>
       <c r="B18" s="23" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="C18" s="26" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="D18" s="26" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="E18" s="26" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="F18" s="53">
         <v>46070</v>
       </c>
       <c r="G18" s="25" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="H18" s="54" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="I18" s="25" t="s">
-        <v>185</v>
-      </c>
-      <c r="J18" s="55" t="s">
-        <v>97</v>
-      </c>
-      <c r="K18" s="28" t="s">
-        <v>78</v>
-      </c>
-      <c r="L18" s="39">
+        <v>180</v>
+      </c>
+      <c r="J18" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="K18" s="39">
         <v>50</v>
       </c>
     </row>
-    <row r="19" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A19" s="23">
         <v>18</v>
       </c>
       <c r="B19" s="23" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="C19" s="23" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="D19" s="26" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="E19" s="26" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="F19" s="53">
         <v>46070</v>
       </c>
       <c r="G19" s="25" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="H19" s="54" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="I19" s="25" t="s">
-        <v>185</v>
-      </c>
-      <c r="J19" s="55" t="s">
-        <v>97</v>
-      </c>
-      <c r="K19" s="28" t="s">
-        <v>78</v>
-      </c>
-      <c r="L19" s="39">
+        <v>180</v>
+      </c>
+      <c r="J19" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="K19" s="39">
         <v>50</v>
       </c>
     </row>
-    <row r="20" spans="1:12" ht="60" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A20" s="23">
         <v>19</v>
       </c>
       <c r="B20" s="23" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="C20" s="23" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="D20" s="26" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E20" s="23" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="F20" s="53">
         <v>46071</v>
       </c>
       <c r="G20" s="25" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="H20" s="54" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="I20" s="25" t="s">
-        <v>112</v>
-      </c>
-      <c r="J20" s="55" t="s">
-        <v>77</v>
-      </c>
-      <c r="K20" s="28" t="s">
-        <v>78</v>
-      </c>
-      <c r="L20" s="39">
+        <v>107</v>
+      </c>
+      <c r="J20" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="K20" s="39">
         <v>37.5</v>
       </c>
     </row>
-    <row r="21" spans="1:12" ht="60" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A21" s="23">
         <v>20</v>
       </c>
       <c r="B21" s="23" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="C21" s="23" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="D21" s="26" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E21" s="23" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="F21" s="53">
         <v>46074</v>
       </c>
       <c r="G21" s="25" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="H21" s="54" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="I21" s="25" t="s">
-        <v>186</v>
-      </c>
-      <c r="J21" s="55" t="s">
-        <v>97</v>
-      </c>
-      <c r="K21" s="28" t="s">
-        <v>78</v>
-      </c>
-      <c r="L21" s="39">
+        <v>181</v>
+      </c>
+      <c r="J21" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="K21" s="39">
         <v>50</v>
       </c>
     </row>
-    <row r="22" spans="1:12" ht="75" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:11" ht="75" x14ac:dyDescent="0.25">
       <c r="A22" s="23">
         <v>21</v>
       </c>
       <c r="B22" s="23" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="C22" s="23" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="D22" s="26" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="E22" s="26" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="F22" s="53">
         <v>46074</v>
       </c>
       <c r="G22" s="25" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="H22" s="54" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="I22" s="25" t="s">
-        <v>188</v>
-      </c>
-      <c r="J22" s="55" t="s">
-        <v>97</v>
-      </c>
-      <c r="K22" s="28" t="s">
-        <v>78</v>
-      </c>
-      <c r="L22" s="39">
+        <v>183</v>
+      </c>
+      <c r="J22" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="K22" s="39">
         <v>50</v>
       </c>
     </row>
-    <row r="23" spans="1:12" ht="60" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A23" s="23">
         <v>22</v>
       </c>
       <c r="B23" s="23" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="C23" s="26" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="D23" s="26" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="E23" s="26" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="F23" s="53">
         <v>46085</v>
       </c>
       <c r="G23" s="25" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H23" s="54" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="I23" s="25" t="s">
-        <v>192</v>
-      </c>
-      <c r="J23" s="55" t="s">
-        <v>97</v>
-      </c>
-      <c r="K23" s="28" t="s">
-        <v>78</v>
-      </c>
-      <c r="L23" s="56">
+        <v>187</v>
+      </c>
+      <c r="J23" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="K23" s="56">
         <v>50</v>
       </c>
     </row>
-    <row r="24" spans="1:12" ht="60" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A24" s="23">
         <v>23</v>
       </c>
       <c r="B24" s="23" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="C24" s="26" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="D24" s="26" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="E24" s="26" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="F24" s="53">
         <v>46086</v>
       </c>
       <c r="G24" s="25" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H24" s="54" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="I24" s="25" t="s">
-        <v>194</v>
-      </c>
-      <c r="J24" s="55" t="s">
-        <v>92</v>
-      </c>
-      <c r="K24" s="28" t="s">
-        <v>78</v>
-      </c>
-      <c r="L24" s="56">
+        <v>189</v>
+      </c>
+      <c r="J24" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="K24" s="56">
         <v>73.75</v>
       </c>
     </row>
-    <row r="25" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A25" s="23">
         <v>24</v>
       </c>
       <c r="B25" s="23" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="C25" s="23" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="D25" s="26" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="E25" s="26" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="F25" s="53">
         <v>46090</v>
       </c>
       <c r="G25" s="25" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H25" s="54" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="I25" s="25" t="s">
-        <v>195</v>
-      </c>
-      <c r="J25" s="55" t="s">
-        <v>97</v>
-      </c>
-      <c r="K25" s="28" t="s">
-        <v>78</v>
-      </c>
-      <c r="L25" s="56">
+        <v>190</v>
+      </c>
+      <c r="J25" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="K25" s="56">
         <v>50</v>
       </c>
     </row>
-    <row r="26" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A26" s="23">
         <v>25</v>
       </c>
       <c r="B26" s="23" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="C26" s="23" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="D26" s="26" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="E26" s="26" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="F26" s="53">
         <v>46091</v>
       </c>
       <c r="G26" s="25" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="H26" s="54" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="I26" s="25" t="s">
-        <v>196</v>
-      </c>
-      <c r="J26" s="55" t="s">
-        <v>77</v>
-      </c>
-      <c r="K26" s="28" t="s">
-        <v>78</v>
-      </c>
-      <c r="L26" s="56">
+        <v>191</v>
+      </c>
+      <c r="J26" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="K26" s="56">
         <v>37.5</v>
       </c>
     </row>
-    <row r="27" spans="1:12" ht="60" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A27" s="23">
         <v>26</v>
       </c>
       <c r="B27" s="23" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="C27" s="23" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="D27" s="26" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E27" s="23" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="F27" s="53">
         <v>46097</v>
       </c>
       <c r="G27" s="25" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="H27" s="54" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="I27" s="25" t="s">
-        <v>186</v>
-      </c>
-      <c r="J27" s="55" t="s">
-        <v>77</v>
-      </c>
-      <c r="K27" s="28" t="s">
-        <v>78</v>
-      </c>
-      <c r="L27" s="56">
+        <v>181</v>
+      </c>
+      <c r="J27" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="K27" s="56">
         <v>37.5</v>
       </c>
     </row>
-    <row r="28" spans="1:12" ht="60" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A28" s="23">
         <v>27</v>
       </c>
       <c r="B28" s="23" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="C28" s="23" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="D28" s="26" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E28" s="23" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="F28" s="53">
         <v>46098</v>
       </c>
       <c r="G28" s="25" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="H28" s="54" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="I28" s="25" t="s">
-        <v>197</v>
-      </c>
-      <c r="J28" s="55" t="s">
-        <v>97</v>
-      </c>
-      <c r="K28" s="28" t="s">
-        <v>78</v>
-      </c>
-      <c r="L28" s="56">
+        <v>192</v>
+      </c>
+      <c r="J28" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="K28" s="56">
         <v>50</v>
       </c>
     </row>
-    <row r="29" spans="1:12" ht="60" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A29" s="23">
         <v>28</v>
       </c>
       <c r="B29" s="23" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="C29" s="55" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="D29" s="26" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="E29" s="26" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="F29" s="53">
         <v>46100</v>
       </c>
       <c r="G29" s="25" t="s">
+        <v>74</v>
+      </c>
+      <c r="H29" s="54" t="s">
         <v>75</v>
       </c>
-      <c r="H29" s="54" t="s">
-        <v>76</v>
-      </c>
       <c r="I29" s="25" t="s">
-        <v>186</v>
-      </c>
-      <c r="J29" s="55" t="s">
-        <v>77</v>
-      </c>
-      <c r="K29" s="28" t="s">
-        <v>78</v>
-      </c>
-      <c r="L29" s="56">
+        <v>181</v>
+      </c>
+      <c r="J29" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="K29" s="56">
         <v>37.5</v>
       </c>
     </row>
-    <row r="30" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A30" s="23">
         <v>29</v>
       </c>
       <c r="B30" s="23" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="C30" s="26" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="D30" s="26" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="E30" s="26" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="F30" s="53">
         <v>46121</v>
       </c>
       <c r="G30" s="25" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H30" s="54" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="I30" s="25" t="s">
-        <v>199</v>
-      </c>
-      <c r="J30" s="55" t="s">
-        <v>97</v>
-      </c>
-      <c r="K30" s="28" t="s">
-        <v>78</v>
-      </c>
-      <c r="L30" s="56">
+        <v>194</v>
+      </c>
+      <c r="J30" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="K30" s="56">
         <v>50</v>
       </c>
     </row>
-    <row r="31" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A31" s="23">
         <v>30</v>
       </c>
       <c r="B31" s="23" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="C31" s="26" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="D31" s="26" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="E31" s="26" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="F31" s="53">
         <v>46127</v>
       </c>
       <c r="G31" s="25" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H31" s="54" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="I31" s="25" t="s">
-        <v>200</v>
-      </c>
-      <c r="J31" s="55" t="s">
-        <v>77</v>
-      </c>
-      <c r="K31" s="28" t="s">
-        <v>78</v>
-      </c>
-      <c r="L31" s="56">
+        <v>195</v>
+      </c>
+      <c r="J31" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="K31" s="56">
         <v>37.5</v>
       </c>
     </row>
-    <row r="32" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A32" s="23">
         <v>31</v>
       </c>
       <c r="B32" s="23" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="C32" s="26" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="D32" s="26" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="E32" s="26" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="F32" s="53">
         <v>46129</v>
       </c>
       <c r="G32" s="25" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H32" s="54" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="I32" s="25" t="s">
-        <v>202</v>
-      </c>
-      <c r="J32" s="55" t="s">
-        <v>97</v>
-      </c>
-      <c r="K32" s="28" t="s">
-        <v>78</v>
-      </c>
-      <c r="L32" s="56">
+        <v>197</v>
+      </c>
+      <c r="J32" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="K32" s="56">
         <v>50</v>
       </c>
     </row>
-    <row r="33" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A33" s="23">
         <v>32</v>
       </c>
       <c r="B33" s="23" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="C33" s="23" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="D33" s="26" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E33" s="26" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="F33" s="53">
         <v>46130</v>
       </c>
       <c r="G33" s="25" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="H33" s="54" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="I33" s="25" t="s">
-        <v>123</v>
-      </c>
-      <c r="J33" s="55" t="s">
-        <v>77</v>
-      </c>
-      <c r="K33" s="28" t="s">
-        <v>78</v>
-      </c>
-      <c r="L33" s="56">
+        <v>118</v>
+      </c>
+      <c r="J33" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="K33" s="56">
         <v>37.5</v>
       </c>
     </row>
-    <row r="34" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A34" s="23">
         <v>33</v>
       </c>
       <c r="B34" s="23" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="C34" s="26" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="D34" s="26" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="E34" s="26" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="F34" s="53">
         <v>46130</v>
       </c>
       <c r="G34" s="25" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H34" s="54" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="I34" s="25" t="s">
-        <v>123</v>
-      </c>
-      <c r="J34" s="55" t="s">
-        <v>77</v>
-      </c>
-      <c r="K34" s="28" t="s">
-        <v>78</v>
-      </c>
-      <c r="L34" s="56">
+        <v>118</v>
+      </c>
+      <c r="J34" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="K34" s="56">
         <v>37.5</v>
       </c>
     </row>
-    <row r="35" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A35" s="23">
         <v>34</v>
       </c>
       <c r="B35" s="23" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="C35" s="23" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="D35" s="26" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="E35" s="26" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="F35" s="53">
         <v>46136</v>
       </c>
       <c r="G35" s="25" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H35" s="54" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="I35" s="25" t="s">
-        <v>123</v>
-      </c>
-      <c r="J35" s="55" t="s">
-        <v>77</v>
-      </c>
-      <c r="K35" s="28" t="s">
-        <v>78</v>
-      </c>
-      <c r="L35" s="56">
+        <v>118</v>
+      </c>
+      <c r="J35" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="K35" s="56">
         <v>37.5</v>
       </c>
     </row>
-    <row r="36" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A36" s="23">
         <v>35</v>
       </c>
       <c r="B36" s="23" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="C36" s="23" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="D36" s="26" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="E36" s="26" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="F36" s="53">
         <v>46137</v>
       </c>
       <c r="G36" s="25" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H36" s="54" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="I36" s="25" t="s">
-        <v>168</v>
-      </c>
-      <c r="J36" s="55" t="s">
-        <v>97</v>
-      </c>
-      <c r="K36" s="28" t="s">
-        <v>78</v>
-      </c>
-      <c r="L36" s="56">
+        <v>163</v>
+      </c>
+      <c r="J36" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="K36" s="56">
         <v>50</v>
       </c>
     </row>
-    <row r="37" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A37" s="23">
         <v>36</v>
       </c>
       <c r="B37" s="23" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="C37" s="26" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="D37" s="26" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="E37" s="26" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="F37" s="53">
         <v>46140</v>
       </c>
       <c r="G37" s="25" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H37" s="54" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="I37" s="25" t="s">
-        <v>203</v>
-      </c>
-      <c r="J37" s="55" t="s">
-        <v>97</v>
-      </c>
-      <c r="K37" s="28" t="s">
-        <v>78</v>
-      </c>
-      <c r="L37" s="56">
+        <v>198</v>
+      </c>
+      <c r="J37" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="K37" s="56">
         <v>50</v>
       </c>
     </row>
-    <row r="38" spans="1:12" ht="60" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A38" s="23">
         <v>37</v>
       </c>
       <c r="B38" s="23" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="C38" s="23" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="D38" s="26" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="E38" s="26" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="F38" s="53">
         <v>46140</v>
       </c>
       <c r="G38" s="25" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H38" s="54" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="I38" s="25" t="s">
-        <v>204</v>
-      </c>
-      <c r="J38" s="55" t="s">
-        <v>97</v>
-      </c>
-      <c r="K38" s="28" t="s">
-        <v>78</v>
-      </c>
-      <c r="L38" s="56">
+        <v>199</v>
+      </c>
+      <c r="J38" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="K38" s="56">
         <v>50</v>
       </c>
     </row>
-    <row r="39" spans="1:12" ht="60" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A39" s="23">
         <v>38</v>
       </c>
       <c r="B39" s="23" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="C39" s="23" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="D39" s="26" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="E39" s="26" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="F39" s="53">
         <v>46146</v>
       </c>
       <c r="G39" s="25" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H39" s="54" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="I39" s="25" t="s">
-        <v>204</v>
-      </c>
-      <c r="J39" s="55" t="s">
-        <v>97</v>
-      </c>
-      <c r="K39" s="28" t="s">
-        <v>78</v>
-      </c>
-      <c r="L39" s="56">
+        <v>199</v>
+      </c>
+      <c r="J39" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="K39" s="56">
         <v>50</v>
       </c>
     </row>
-    <row r="40" spans="1:12" ht="60" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A40" s="23">
         <v>39</v>
       </c>
       <c r="B40" s="23" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="C40" s="26" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="D40" s="26" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="E40" s="26" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="F40" s="53">
         <v>46147</v>
       </c>
       <c r="G40" s="25" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H40" s="54" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="I40" s="25" t="s">
-        <v>194</v>
-      </c>
-      <c r="J40" s="55" t="s">
-        <v>97</v>
-      </c>
-      <c r="K40" s="28" t="s">
-        <v>78</v>
-      </c>
-      <c r="L40" s="56">
+        <v>189</v>
+      </c>
+      <c r="J40" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="K40" s="56">
         <v>50</v>
       </c>
     </row>
-    <row r="41" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A41" s="23">
         <v>40</v>
       </c>
       <c r="B41" s="23" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="C41" s="26" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="D41" s="26" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="E41" s="26" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="F41" s="53">
         <v>46164</v>
       </c>
       <c r="G41" s="25" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H41" s="54" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="I41" s="25" t="s">
-        <v>123</v>
-      </c>
-      <c r="J41" s="55" t="s">
-        <v>77</v>
-      </c>
-      <c r="K41" s="28" t="s">
-        <v>78</v>
-      </c>
-      <c r="L41" s="56">
+        <v>118</v>
+      </c>
+      <c r="J41" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="K41" s="56">
         <v>37.5</v>
       </c>
     </row>
-    <row r="42" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A42" s="23">
         <v>41</v>
       </c>
       <c r="B42" s="23" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="C42" s="26" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="D42" s="26" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="E42" s="26" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="F42" s="53">
         <v>46167</v>
       </c>
       <c r="G42" s="25" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H42" s="54" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="I42" s="25" t="s">
-        <v>123</v>
-      </c>
-      <c r="J42" s="55" t="s">
-        <v>77</v>
-      </c>
-      <c r="K42" s="28" t="s">
-        <v>78</v>
-      </c>
-      <c r="L42" s="56">
+        <v>118</v>
+      </c>
+      <c r="J42" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="K42" s="56">
         <v>37.5</v>
       </c>
     </row>
-    <row r="43" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A43" s="23">
         <v>42</v>
       </c>
       <c r="B43" s="23" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="C43" s="23" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="D43" s="26" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="E43" s="26" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="F43" s="53">
         <v>46170</v>
       </c>
       <c r="G43" s="25" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="H43" s="54" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="I43" s="25" t="s">
-        <v>123</v>
-      </c>
-      <c r="J43" s="55" t="s">
-        <v>77</v>
-      </c>
-      <c r="K43" s="28" t="s">
-        <v>78</v>
-      </c>
-      <c r="L43" s="56">
+        <v>118</v>
+      </c>
+      <c r="J43" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="K43" s="56">
         <v>37.5</v>
       </c>
     </row>
-    <row r="44" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A44" s="23">
         <v>43</v>
       </c>
       <c r="B44" s="50" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="C44" s="51" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="D44" s="51" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="E44" s="51" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="F44" s="57">
         <v>46191</v>
       </c>
       <c r="G44" s="25" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="H44" s="54" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="I44" s="25" t="s">
-        <v>223</v>
-      </c>
-      <c r="J44" s="55" t="s">
-        <v>97</v>
-      </c>
-      <c r="K44" s="28" t="s">
-        <v>78</v>
-      </c>
-      <c r="L44" s="58">
+        <v>218</v>
+      </c>
+      <c r="J44" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="K44" s="58">
         <v>50</v>
       </c>
     </row>
-    <row r="45" spans="1:12" ht="75" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:11" ht="75" x14ac:dyDescent="0.25">
       <c r="A45" s="23">
         <v>44</v>
       </c>
       <c r="B45" s="23" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="C45" s="26" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="D45" s="26" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="E45" s="26" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="F45" s="53">
         <v>46196</v>
       </c>
       <c r="G45" s="25" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H45" s="54" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="I45" s="25" t="s">
-        <v>224</v>
-      </c>
-      <c r="J45" s="55" t="s">
-        <v>77</v>
-      </c>
-      <c r="K45" s="28" t="s">
-        <v>78</v>
-      </c>
-      <c r="L45" s="58">
+        <v>219</v>
+      </c>
+      <c r="J45" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="K45" s="58">
         <v>37.5</v>
       </c>
     </row>
-    <row r="46" spans="1:12" ht="60" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A46" s="23">
         <v>45</v>
       </c>
       <c r="B46" s="23" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="C46" s="26" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="D46" s="26" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="E46" s="26" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="F46" s="53">
         <v>46197</v>
       </c>
       <c r="G46" s="25" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H46" s="54" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="I46" s="25" t="s">
-        <v>194</v>
-      </c>
-      <c r="J46" s="55" t="s">
-        <v>97</v>
-      </c>
-      <c r="K46" s="28" t="s">
-        <v>78</v>
-      </c>
-      <c r="L46" s="58">
+        <v>189</v>
+      </c>
+      <c r="J46" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="K46" s="58">
         <v>50</v>
       </c>
     </row>
-    <row r="47" spans="1:12" ht="75" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:11" ht="75" x14ac:dyDescent="0.25">
       <c r="A47" s="23">
         <v>46</v>
       </c>
       <c r="B47" s="23" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="C47" s="23" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="D47" s="26" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E47" s="26" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="F47" s="53">
         <v>46211</v>
       </c>
       <c r="G47" s="25" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="H47" s="54" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="I47" s="25" t="s">
-        <v>224</v>
-      </c>
-      <c r="J47" s="55" t="s">
-        <v>77</v>
-      </c>
-      <c r="K47" s="28" t="s">
-        <v>78</v>
-      </c>
-      <c r="L47" s="58">
+        <v>219</v>
+      </c>
+      <c r="J47" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="K47" s="58">
         <v>37.5</v>
       </c>
     </row>
-    <row r="48" spans="1:12" ht="75" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:11" ht="75" x14ac:dyDescent="0.25">
       <c r="A48" s="23">
         <v>47</v>
       </c>
       <c r="B48" s="23" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="C48" s="23" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="D48" s="26" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E48" s="26" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="F48" s="53">
         <v>46220</v>
       </c>
       <c r="G48" s="25" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="H48" s="54" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="I48" s="25" t="s">
-        <v>226</v>
-      </c>
-      <c r="J48" s="55" t="s">
-        <v>97</v>
-      </c>
-      <c r="K48" s="28" t="s">
-        <v>78</v>
-      </c>
-      <c r="L48" s="58">
+        <v>221</v>
+      </c>
+      <c r="J48" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="K48" s="58">
         <v>50</v>
       </c>
     </row>
-    <row r="49" spans="1:12" ht="75" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:11" ht="75" x14ac:dyDescent="0.25">
       <c r="A49" s="23">
         <v>48</v>
       </c>
       <c r="B49" s="23" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="C49" s="23" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="D49" s="26" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E49" s="26" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="F49" s="53">
         <v>46220</v>
       </c>
       <c r="G49" s="25" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="H49" s="54" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="I49" s="25" t="s">
-        <v>226</v>
-      </c>
-      <c r="J49" s="55" t="s">
-        <v>97</v>
-      </c>
-      <c r="K49" s="28" t="s">
-        <v>78</v>
-      </c>
-      <c r="L49" s="58">
+        <v>221</v>
+      </c>
+      <c r="J49" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="K49" s="58">
         <v>50</v>
       </c>
     </row>
-    <row r="50" spans="1:12" ht="75" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:11" ht="75" x14ac:dyDescent="0.25">
       <c r="A50" s="23">
         <v>49</v>
       </c>
       <c r="B50" s="23" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="C50" s="26" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="D50" s="26" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E50" s="26" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="F50" s="53">
         <v>46235</v>
       </c>
       <c r="G50" s="25" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H50" s="54" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="I50" s="25" t="s">
-        <v>123</v>
-      </c>
-      <c r="J50" s="55" t="s">
-        <v>77</v>
-      </c>
-      <c r="K50" s="28" t="s">
-        <v>78</v>
-      </c>
-      <c r="L50" s="58">
+        <v>118</v>
+      </c>
+      <c r="J50" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="K50" s="58">
         <v>37.5</v>
       </c>
     </row>
-    <row r="51" spans="1:12" ht="75" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:11" ht="75" x14ac:dyDescent="0.25">
       <c r="A51" s="23">
         <v>50</v>
       </c>
       <c r="B51" s="23" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="C51" s="26" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="D51" s="26" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E51" s="26" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="F51" s="53">
         <v>46241</v>
       </c>
       <c r="G51" s="25" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H51" s="54" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="I51" s="25" t="s">
-        <v>123</v>
-      </c>
-      <c r="J51" s="55" t="s">
-        <v>77</v>
-      </c>
-      <c r="K51" s="28" t="s">
-        <v>78</v>
-      </c>
-      <c r="L51" s="58">
+        <v>118</v>
+      </c>
+      <c r="J51" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="K51" s="58">
         <v>37.5</v>
       </c>
     </row>
-    <row r="52" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A52" s="23">
         <v>51</v>
       </c>
       <c r="B52" s="23" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="C52" s="26" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="D52" s="26" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="E52" s="26" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="F52" s="53">
         <v>46255</v>
       </c>
       <c r="G52" s="25" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H52" s="54" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="I52" s="25" t="s">
-        <v>123</v>
-      </c>
-      <c r="J52" s="55" t="s">
-        <v>77</v>
-      </c>
-      <c r="K52" s="28" t="s">
-        <v>78</v>
-      </c>
-      <c r="L52" s="58">
+        <v>118</v>
+      </c>
+      <c r="J52" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="K52" s="58">
         <v>37.5</v>
       </c>
     </row>
-    <row r="53" spans="1:12" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:11" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="23">
         <v>52</v>
       </c>
       <c r="B53" s="26" t="s">
-        <v>151</v>
+        <v>200</v>
       </c>
       <c r="C53" s="26" t="s">
-        <v>93</v>
+        <v>146</v>
       </c>
       <c r="D53" s="26" t="s">
-        <v>152</v>
+        <v>89</v>
       </c>
       <c r="E53" s="26" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="F53" s="54">
         <v>46258</v>
       </c>
       <c r="G53" s="25" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H53" s="54" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="I53" s="25" t="s">
-        <v>229</v>
-      </c>
-      <c r="J53" s="59" t="s">
-        <v>97</v>
-      </c>
-      <c r="K53" s="28" t="s">
-        <v>78</v>
-      </c>
-      <c r="L53" s="39">
+        <v>224</v>
+      </c>
+      <c r="J53" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="K53" s="39">
         <v>50</v>
       </c>
     </row>
-    <row r="54" spans="1:12" ht="48.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:11" ht="48.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="23">
         <v>53</v>
       </c>
       <c r="B54" s="26" t="s">
-        <v>155</v>
+        <v>200</v>
       </c>
       <c r="C54" s="26" t="s">
-        <v>87</v>
+        <v>150</v>
       </c>
       <c r="D54" s="26" t="s">
-        <v>156</v>
+        <v>84</v>
       </c>
       <c r="E54" s="26" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="F54" s="54">
         <v>46259</v>
       </c>
       <c r="G54" s="25" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H54" s="54" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="I54" s="25" t="s">
-        <v>204</v>
-      </c>
-      <c r="J54" s="59" t="s">
-        <v>97</v>
-      </c>
-      <c r="K54" s="28" t="s">
-        <v>78</v>
-      </c>
-      <c r="L54" s="39">
+        <v>199</v>
+      </c>
+      <c r="J54" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="K54" s="39">
         <v>50</v>
       </c>
     </row>
-    <row r="55" spans="1:12" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:11" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="23">
         <v>54</v>
       </c>
       <c r="B55" s="26" t="s">
-        <v>151</v>
+        <v>200</v>
       </c>
       <c r="C55" s="26" t="s">
-        <v>93</v>
+        <v>146</v>
       </c>
       <c r="D55" s="26" t="s">
-        <v>152</v>
+        <v>89</v>
       </c>
       <c r="E55" s="26" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="F55" s="54">
         <v>46262</v>
       </c>
       <c r="G55" s="25" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H55" s="54" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="I55" s="25" t="s">
-        <v>231</v>
-      </c>
-      <c r="J55" s="59" t="s">
-        <v>97</v>
-      </c>
-      <c r="K55" s="28" t="s">
-        <v>78</v>
-      </c>
-      <c r="L55" s="39">
+        <v>226</v>
+      </c>
+      <c r="J55" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="K55" s="39">
         <v>50</v>
       </c>
     </row>
-    <row r="56" spans="1:12" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:11" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="23">
         <v>55</v>
       </c>
       <c r="B56" s="26" t="s">
-        <v>155</v>
+        <v>200</v>
       </c>
       <c r="C56" s="26" t="s">
-        <v>87</v>
+        <v>150</v>
       </c>
       <c r="D56" s="26" t="s">
-        <v>156</v>
+        <v>84</v>
       </c>
       <c r="E56" s="26" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="F56" s="54">
         <v>46263</v>
       </c>
       <c r="G56" s="25" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H56" s="54" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="I56" s="25" t="s">
-        <v>185</v>
-      </c>
-      <c r="J56" s="59" t="s">
-        <v>97</v>
-      </c>
-      <c r="K56" s="28" t="s">
-        <v>78</v>
-      </c>
-      <c r="L56" s="39">
+        <v>180</v>
+      </c>
+      <c r="J56" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="K56" s="39">
         <v>50</v>
       </c>
     </row>
-    <row r="57" spans="1:12" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:11" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="23">
         <v>56</v>
       </c>
       <c r="B57" s="26" t="s">
-        <v>147</v>
+        <v>200</v>
       </c>
       <c r="C57" s="26" t="s">
-        <v>83</v>
+        <v>142</v>
       </c>
       <c r="D57" s="26" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="E57" s="26" t="s">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="F57" s="54">
         <v>46266</v>
       </c>
       <c r="G57" s="25" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="H57" s="54" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="I57" s="25" t="s">
-        <v>123</v>
-      </c>
-      <c r="J57" s="59" t="s">
-        <v>77</v>
-      </c>
-      <c r="K57" s="28" t="s">
-        <v>78</v>
-      </c>
-      <c r="L57" s="60">
+        <v>118</v>
+      </c>
+      <c r="J57" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="K57" s="59">
         <v>37.5</v>
       </c>
     </row>
-    <row r="58" spans="1:12" ht="39" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:11" ht="39" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="23">
         <v>57</v>
       </c>
       <c r="B58" s="26" t="s">
-        <v>155</v>
+        <v>200</v>
       </c>
       <c r="C58" s="26" t="s">
-        <v>87</v>
+        <v>150</v>
       </c>
       <c r="D58" s="26" t="s">
-        <v>156</v>
+        <v>84</v>
       </c>
       <c r="E58" s="26" t="s">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="F58" s="54">
         <v>46274</v>
       </c>
       <c r="G58" s="25" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H58" s="54" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="I58" s="25" t="s">
-        <v>231</v>
-      </c>
-      <c r="J58" s="59" t="s">
-        <v>97</v>
-      </c>
-      <c r="K58" s="28" t="s">
-        <v>78</v>
-      </c>
-      <c r="L58" s="39">
+        <v>226</v>
+      </c>
+      <c r="J58" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="K58" s="39">
         <v>50</v>
       </c>
     </row>
-    <row r="59" spans="1:12" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:11" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="23">
         <v>58</v>
       </c>
       <c r="B59" s="26" t="s">
+        <v>201</v>
+      </c>
+      <c r="C59" s="26" t="s">
+        <v>222</v>
+      </c>
+      <c r="D59" s="26" t="s">
+        <v>71</v>
+      </c>
+      <c r="E59" s="26" t="s">
         <v>227</v>
-      </c>
-      <c r="C59" s="26" t="s">
-        <v>72</v>
-      </c>
-      <c r="D59" s="26" t="s">
-        <v>73</v>
-      </c>
-      <c r="E59" s="26" t="s">
-        <v>232</v>
       </c>
       <c r="F59" s="54">
         <v>46279</v>
       </c>
       <c r="G59" s="25" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H59" s="54" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="I59" s="25" t="s">
-        <v>234</v>
-      </c>
-      <c r="J59" s="59" t="s">
-        <v>97</v>
-      </c>
-      <c r="K59" s="28" t="s">
-        <v>78</v>
-      </c>
-      <c r="L59" s="39">
+        <v>229</v>
+      </c>
+      <c r="J59" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="K59" s="39">
         <v>50</v>
       </c>
     </row>
-    <row r="60" spans="1:12" ht="48.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:11" ht="48.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="23">
         <v>59</v>
       </c>
       <c r="B60" s="26" t="s">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="C60" s="26" t="s">
-        <v>83</v>
+        <v>145</v>
       </c>
       <c r="D60" s="26" t="s">
-        <v>95</v>
+        <v>81</v>
       </c>
       <c r="E60" s="26" t="s">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="F60" s="54">
         <v>46283</v>
       </c>
       <c r="G60" s="25" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="H60" s="54" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="I60" s="25" t="s">
-        <v>236</v>
-      </c>
-      <c r="J60" s="59" t="s">
-        <v>97</v>
-      </c>
-      <c r="K60" s="28" t="s">
-        <v>78</v>
-      </c>
-      <c r="L60" s="39">
+        <v>231</v>
+      </c>
+      <c r="J60" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="K60" s="39">
         <v>50</v>
       </c>
     </row>
-    <row r="61" spans="1:12" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:11" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="23">
         <v>60</v>
       </c>
       <c r="B61" s="26" t="s">
-        <v>237</v>
+        <v>200</v>
       </c>
       <c r="C61" s="26" t="s">
-        <v>72</v>
+        <v>232</v>
       </c>
       <c r="D61" s="26" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E61" s="26" t="s">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="F61" s="54">
         <v>46288</v>
       </c>
       <c r="G61" s="25" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H61" s="54" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="I61" s="25" t="s">
-        <v>236</v>
-      </c>
-      <c r="J61" s="59" t="s">
-        <v>97</v>
-      </c>
-      <c r="K61" s="28" t="s">
-        <v>78</v>
-      </c>
-      <c r="L61" s="39">
+        <v>231</v>
+      </c>
+      <c r="J61" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="K61" s="39">
         <v>50</v>
       </c>
     </row>
-    <row r="62" spans="1:12" ht="54.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:11" ht="54.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="23">
         <v>61</v>
       </c>
       <c r="B62" s="26" t="s">
-        <v>172</v>
+        <v>200</v>
       </c>
       <c r="C62" s="26" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="D62" s="26" t="s">
-        <v>238</v>
+        <v>168</v>
       </c>
       <c r="E62" s="26" t="s">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="F62" s="54">
         <v>46291</v>
       </c>
       <c r="G62" s="25" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H62" s="54" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="I62" s="25" t="s">
-        <v>143</v>
-      </c>
-      <c r="J62" s="59" t="s">
-        <v>97</v>
-      </c>
-      <c r="K62" s="28" t="s">
-        <v>78</v>
-      </c>
-      <c r="L62" s="39">
+        <v>138</v>
+      </c>
+      <c r="J62" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="K62" s="39">
         <v>50</v>
       </c>
     </row>
-    <row r="63" spans="1:12" ht="64.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:11" ht="64.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="23">
         <v>62</v>
       </c>
       <c r="B63" s="26" t="s">
-        <v>148</v>
+        <v>200</v>
       </c>
       <c r="C63" s="26" t="s">
-        <v>81</v>
+        <v>143</v>
       </c>
       <c r="D63" s="26" t="s">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="E63" s="26" t="s">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="F63" s="54">
         <v>46294</v>
       </c>
       <c r="G63" s="25" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="H63" s="54" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="I63" s="25" t="s">
-        <v>236</v>
-      </c>
-      <c r="J63" s="59" t="s">
-        <v>97</v>
-      </c>
-      <c r="K63" s="28" t="s">
-        <v>78</v>
-      </c>
-      <c r="L63" s="60">
+        <v>231</v>
+      </c>
+      <c r="J63" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="K63" s="59">
         <v>50</v>
       </c>
     </row>
-    <row r="64" spans="1:12" ht="55.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:11" ht="55.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="23">
         <v>63</v>
       </c>
       <c r="B64" s="26" t="s">
-        <v>147</v>
+        <v>200</v>
       </c>
       <c r="C64" s="26" t="s">
-        <v>83</v>
+        <v>142</v>
       </c>
       <c r="D64" s="26" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="E64" s="26" t="s">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="F64" s="54">
         <v>46295</v>
       </c>
       <c r="G64" s="25" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="H64" s="54" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="I64" s="25" t="s">
-        <v>236</v>
-      </c>
-      <c r="J64" s="59" t="s">
-        <v>97</v>
-      </c>
-      <c r="K64" s="28" t="s">
-        <v>78</v>
-      </c>
-      <c r="L64" s="39">
+        <v>231</v>
+      </c>
+      <c r="J64" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="K64" s="39">
         <v>50</v>
       </c>
     </row>
@@ -9030,22 +8533,22 @@
   <sheetData>
     <row r="1" spans="1:6" s="41" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="45" t="s">
+        <v>202</v>
+      </c>
+      <c r="B1" s="45" t="s">
+        <v>203</v>
+      </c>
+      <c r="C1" s="45" t="s">
+        <v>204</v>
+      </c>
+      <c r="D1" s="45" t="s">
+        <v>205</v>
+      </c>
+      <c r="E1" s="45" t="s">
+        <v>206</v>
+      </c>
+      <c r="F1" s="45" t="s">
         <v>207</v>
-      </c>
-      <c r="B1" s="45" t="s">
-        <v>208</v>
-      </c>
-      <c r="C1" s="45" t="s">
-        <v>209</v>
-      </c>
-      <c r="D1" s="45" t="s">
-        <v>210</v>
-      </c>
-      <c r="E1" s="45" t="s">
-        <v>211</v>
-      </c>
-      <c r="F1" s="45" t="s">
-        <v>212</v>
       </c>
     </row>
     <row r="2" spans="1:6" s="42" customFormat="1" x14ac:dyDescent="0.25">
@@ -9053,10 +8556,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="46" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="C2" s="46" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="D2" s="46">
         <v>1</v>
@@ -9074,10 +8577,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="48" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="C3" s="48" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="D3" s="48">
         <v>1</v>
@@ -9095,10 +8598,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="46" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="C4" s="46" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="D4" s="46">
         <v>1</v>
@@ -9116,10 +8619,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="48" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="C5" s="48" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="D5" s="48">
         <v>1</v>
@@ -9137,19 +8640,19 @@
         <v>5</v>
       </c>
       <c r="B6" s="27" t="s">
-        <v>243</v>
+        <v>237</v>
       </c>
       <c r="C6" s="27" t="s">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="D6" s="27">
         <v>1</v>
       </c>
       <c r="E6" s="27" t="s">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="F6" s="27" t="s">
-        <v>242</v>
+        <v>236</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -9157,19 +8660,19 @@
         <v>6</v>
       </c>
       <c r="B7" s="27" t="s">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="C7" s="27" t="s">
-        <v>245</v>
+        <v>239</v>
       </c>
       <c r="D7" s="27">
         <v>1</v>
       </c>
       <c r="E7" s="27" t="s">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="F7" s="27" t="s">
-        <v>247</v>
+        <v>241</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">

--- a/DRIVE TRHU BASE.xlsx
+++ b/DRIVE TRHU BASE.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="8910" activeTab="2"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="8910"/>
   </bookViews>
   <sheets>
     <sheet name="Drive HME" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1621" uniqueCount="245">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1631" uniqueCount="246">
   <si>
     <t>N°</t>
   </si>
@@ -760,6 +760,9 @@
   </si>
   <si>
     <t xml:space="preserve">cambio de cargador de baterias </t>
+  </si>
+  <si>
+    <t>STB134</t>
   </si>
 </sst>
 </file>
@@ -1443,7 +1446,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Z12"/>
+  <dimension ref="A1:Z13"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="2.7109375" style="1" bestFit="1" customWidth="1"/>
@@ -2405,6 +2408,86 @@
       </c>
       <c r="Y12" s="31"/>
       <c r="Z12" s="31" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="13" spans="1:26" s="32" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="29">
+        <v>12</v>
+      </c>
+      <c r="B13" s="29" t="s">
+        <v>35</v>
+      </c>
+      <c r="C13" s="29" t="s">
+        <v>245</v>
+      </c>
+      <c r="D13" s="29" t="s">
+        <v>38</v>
+      </c>
+      <c r="E13" s="30">
+        <v>4</v>
+      </c>
+      <c r="F13" s="30">
+        <v>2</v>
+      </c>
+      <c r="G13" s="30">
+        <f t="shared" ref="G13" si="2">E13+F13</f>
+        <v>6</v>
+      </c>
+      <c r="H13" s="30">
+        <v>1</v>
+      </c>
+      <c r="I13" s="30" t="s">
+        <v>23</v>
+      </c>
+      <c r="J13" s="31">
+        <v>7</v>
+      </c>
+      <c r="K13" s="31">
+        <v>1</v>
+      </c>
+      <c r="L13" s="31">
+        <f t="shared" ref="L13" si="3">J13+K13</f>
+        <v>8</v>
+      </c>
+      <c r="M13" s="30">
+        <v>1</v>
+      </c>
+      <c r="N13" s="30" t="s">
+        <v>23</v>
+      </c>
+      <c r="O13" s="30">
+        <v>1</v>
+      </c>
+      <c r="P13" s="30" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q13" s="30">
+        <v>1</v>
+      </c>
+      <c r="R13" s="30" t="s">
+        <v>23</v>
+      </c>
+      <c r="S13" s="30">
+        <v>4</v>
+      </c>
+      <c r="T13" s="30">
+        <v>1</v>
+      </c>
+      <c r="U13" s="30">
+        <v>1</v>
+      </c>
+      <c r="V13" s="30">
+        <v>1</v>
+      </c>
+      <c r="W13" s="30" t="s">
+        <v>23</v>
+      </c>
+      <c r="X13" s="31" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y13" s="31"/>
+      <c r="Z13" s="31" t="s">
         <v>58</v>
       </c>
     </row>

--- a/DRIVE TRHU BASE.xlsx
+++ b/DRIVE TRHU BASE.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1631" uniqueCount="246">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1621" uniqueCount="245">
   <si>
     <t>N°</t>
   </si>
@@ -760,9 +760,6 @@
   </si>
   <si>
     <t xml:space="preserve">cambio de cargador de baterias </t>
-  </si>
-  <si>
-    <t>STB134</t>
   </si>
 </sst>
 </file>
@@ -1446,7 +1443,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Z13"/>
+  <dimension ref="A1:Z12"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="2.7109375" style="1" bestFit="1" customWidth="1"/>
@@ -2408,86 +2405,6 @@
       </c>
       <c r="Y12" s="31"/>
       <c r="Z12" s="31" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="13" spans="1:26" s="32" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="29">
-        <v>12</v>
-      </c>
-      <c r="B13" s="29" t="s">
-        <v>35</v>
-      </c>
-      <c r="C13" s="29" t="s">
-        <v>245</v>
-      </c>
-      <c r="D13" s="29" t="s">
-        <v>38</v>
-      </c>
-      <c r="E13" s="30">
-        <v>4</v>
-      </c>
-      <c r="F13" s="30">
-        <v>2</v>
-      </c>
-      <c r="G13" s="30">
-        <f t="shared" ref="G13" si="2">E13+F13</f>
-        <v>6</v>
-      </c>
-      <c r="H13" s="30">
-        <v>1</v>
-      </c>
-      <c r="I13" s="30" t="s">
-        <v>23</v>
-      </c>
-      <c r="J13" s="31">
-        <v>7</v>
-      </c>
-      <c r="K13" s="31">
-        <v>1</v>
-      </c>
-      <c r="L13" s="31">
-        <f t="shared" ref="L13" si="3">J13+K13</f>
-        <v>8</v>
-      </c>
-      <c r="M13" s="30">
-        <v>1</v>
-      </c>
-      <c r="N13" s="30" t="s">
-        <v>23</v>
-      </c>
-      <c r="O13" s="30">
-        <v>1</v>
-      </c>
-      <c r="P13" s="30" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q13" s="30">
-        <v>1</v>
-      </c>
-      <c r="R13" s="30" t="s">
-        <v>23</v>
-      </c>
-      <c r="S13" s="30">
-        <v>4</v>
-      </c>
-      <c r="T13" s="30">
-        <v>1</v>
-      </c>
-      <c r="U13" s="30">
-        <v>1</v>
-      </c>
-      <c r="V13" s="30">
-        <v>1</v>
-      </c>
-      <c r="W13" s="30" t="s">
-        <v>23</v>
-      </c>
-      <c r="X13" s="31" t="s">
-        <v>23</v>
-      </c>
-      <c r="Y13" s="31"/>
-      <c r="Z13" s="31" t="s">
         <v>58</v>
       </c>
     </row>
